--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216535</v>
+        <v>121216502</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>90687</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511681</v>
+        <v>511691</v>
       </c>
       <c r="R3" t="n">
         <v>6733814</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216577</v>
+        <v>121216583</v>
       </c>
       <c r="B4" t="n">
-        <v>100337</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511753</v>
+        <v>511712</v>
       </c>
       <c r="R4" t="n">
-        <v>6733916</v>
+        <v>6733841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216580</v>
+        <v>121216577</v>
       </c>
       <c r="B5" t="n">
         <v>100337</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511773</v>
+        <v>511753</v>
       </c>
       <c r="R5" t="n">
-        <v>6733953</v>
+        <v>6733916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216502</v>
+        <v>121216580</v>
       </c>
       <c r="B6" t="n">
-        <v>90687</v>
+        <v>100337</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511691</v>
+        <v>511773</v>
       </c>
       <c r="R6" t="n">
-        <v>6733814</v>
+        <v>6733953</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216583</v>
+        <v>121216535</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>90973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,43 +1202,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511712</v>
+        <v>511681</v>
       </c>
       <c r="R7" t="n">
-        <v>6733841</v>
+        <v>6733814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216551</v>
+        <v>121216503</v>
       </c>
       <c r="B15" t="n">
-        <v>90705</v>
+        <v>90687</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511719</v>
+        <v>511689</v>
       </c>
       <c r="R15" t="n">
-        <v>6733835</v>
+        <v>6733823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216526</v>
+        <v>121216504</v>
       </c>
       <c r="B16" t="n">
-        <v>91127</v>
+        <v>90687</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511715</v>
+        <v>511683</v>
       </c>
       <c r="R16" t="n">
-        <v>6733819</v>
+        <v>6733814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216503</v>
+        <v>121216551</v>
       </c>
       <c r="B17" t="n">
-        <v>90687</v>
+        <v>90705</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511689</v>
+        <v>511719</v>
       </c>
       <c r="R17" t="n">
-        <v>6733823</v>
+        <v>6733835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216504</v>
+        <v>121216526</v>
       </c>
       <c r="B18" t="n">
-        <v>90687</v>
+        <v>91127</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511683</v>
+        <v>511715</v>
       </c>
       <c r="R18" t="n">
-        <v>6733814</v>
+        <v>6733819</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216493</v>
+        <v>121216568</v>
       </c>
       <c r="B53" t="n">
-        <v>95618</v>
+        <v>100337</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511719</v>
+        <v>511706</v>
       </c>
       <c r="R53" t="n">
-        <v>6733820</v>
+        <v>6733883</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216536</v>
+        <v>121216493</v>
       </c>
       <c r="B54" t="n">
-        <v>90973</v>
+        <v>95618</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511766</v>
+        <v>511719</v>
       </c>
       <c r="R54" t="n">
-        <v>6733889</v>
+        <v>6733820</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216568</v>
+        <v>121216536</v>
       </c>
       <c r="B55" t="n">
-        <v>100337</v>
+        <v>90973</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,25 +6113,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511706</v>
+        <v>511766</v>
       </c>
       <c r="R55" t="n">
-        <v>6733883</v>
+        <v>6733889</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216559</v>
+        <v>121216508</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511701</v>
+        <v>511778</v>
       </c>
       <c r="R2" t="n">
-        <v>6733806</v>
+        <v>6733888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216502</v>
+        <v>121216577</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511691</v>
+        <v>511753</v>
       </c>
       <c r="R3" t="n">
-        <v>6733814</v>
+        <v>6733916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216583</v>
+        <v>121216536</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511712</v>
+        <v>511766</v>
       </c>
       <c r="R4" t="n">
-        <v>6733841</v>
+        <v>6733889</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216577</v>
+        <v>121216501</v>
       </c>
       <c r="B5" t="n">
-        <v>100337</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511753</v>
+        <v>511692</v>
       </c>
       <c r="R5" t="n">
-        <v>6733916</v>
+        <v>6733805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216580</v>
+        <v>121216552</v>
       </c>
       <c r="B6" t="n">
-        <v>100337</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511773</v>
+        <v>511717</v>
       </c>
       <c r="R6" t="n">
-        <v>6733953</v>
+        <v>6733907</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216535</v>
+        <v>121216520</v>
       </c>
       <c r="B7" t="n">
-        <v>90973</v>
+        <v>91137</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511681</v>
+        <v>511694</v>
       </c>
       <c r="R7" t="n">
-        <v>6733814</v>
+        <v>6733776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1295,7 +1290,7 @@
         <v>121216534</v>
       </c>
       <c r="B8" t="n">
-        <v>90973</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216494</v>
+        <v>121216519</v>
       </c>
       <c r="B9" t="n">
-        <v>90652</v>
+        <v>91137</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511695</v>
+        <v>511684</v>
       </c>
       <c r="R9" t="n">
-        <v>6733800</v>
+        <v>6733782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216570</v>
+        <v>121216495</v>
       </c>
       <c r="B10" t="n">
-        <v>100337</v>
+        <v>90662</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511737</v>
+        <v>511704</v>
       </c>
       <c r="R10" t="n">
-        <v>6733875</v>
+        <v>6733869</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216572</v>
+        <v>121216493</v>
       </c>
       <c r="B11" t="n">
-        <v>100337</v>
+        <v>95628</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511717</v>
+        <v>511719</v>
       </c>
       <c r="R11" t="n">
-        <v>6733894</v>
+        <v>6733820</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,7 +1658,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216578</v>
+        <v>121216571</v>
       </c>
       <c r="B12" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511790</v>
+        <v>511735</v>
       </c>
       <c r="R12" t="n">
-        <v>6733915</v>
+        <v>6733890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1760,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216525</v>
+        <v>121216524</v>
       </c>
       <c r="B13" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511722</v>
+        <v>511679</v>
       </c>
       <c r="R13" t="n">
-        <v>6733810</v>
+        <v>6733815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216522</v>
+        <v>121216569</v>
       </c>
       <c r="B14" t="n">
-        <v>91127</v>
+        <v>100347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511691</v>
+        <v>511726</v>
       </c>
       <c r="R14" t="n">
-        <v>6733814</v>
+        <v>6733897</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216503</v>
+        <v>121216544</v>
       </c>
       <c r="B15" t="n">
-        <v>90687</v>
+        <v>90711</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511689</v>
+        <v>511752</v>
       </c>
       <c r="R15" t="n">
-        <v>6733823</v>
+        <v>6733939</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,6 +2077,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216504</v>
+        <v>121216553</v>
       </c>
       <c r="B16" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511683</v>
+        <v>511738</v>
       </c>
       <c r="R16" t="n">
-        <v>6733814</v>
+        <v>6733948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216551</v>
+        <v>121216573</v>
       </c>
       <c r="B17" t="n">
-        <v>90705</v>
+        <v>100347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511719</v>
+        <v>511712</v>
       </c>
       <c r="R17" t="n">
-        <v>6733835</v>
+        <v>6733910</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216526</v>
+        <v>121216525</v>
       </c>
       <c r="B18" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511715</v>
+        <v>511722</v>
       </c>
       <c r="R18" t="n">
-        <v>6733819</v>
+        <v>6733810</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216529</v>
+        <v>121216559</v>
       </c>
       <c r="B19" t="n">
-        <v>91127</v>
+        <v>100347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511778</v>
+        <v>511701</v>
       </c>
       <c r="R19" t="n">
-        <v>6733902</v>
+        <v>6733806</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216566</v>
+        <v>121216505</v>
       </c>
       <c r="B20" t="n">
-        <v>100337</v>
+        <v>90697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511692</v>
+        <v>511703</v>
       </c>
       <c r="R20" t="n">
-        <v>6733799</v>
+        <v>6733823</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216576</v>
+        <v>121216545</v>
       </c>
       <c r="B21" t="n">
-        <v>100337</v>
+        <v>90711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511735</v>
+        <v>511749</v>
       </c>
       <c r="R21" t="n">
-        <v>6733932</v>
+        <v>6733943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2694,6 +2694,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216565</v>
+        <v>121216550</v>
       </c>
       <c r="B22" t="n">
-        <v>100337</v>
+        <v>90715</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511692</v>
+        <v>511697</v>
       </c>
       <c r="R22" t="n">
-        <v>6733786</v>
+        <v>6733776</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216495</v>
+        <v>121216572</v>
       </c>
       <c r="B23" t="n">
-        <v>90652</v>
+        <v>100347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511704</v>
+        <v>511717</v>
       </c>
       <c r="R23" t="n">
-        <v>6733869</v>
+        <v>6733894</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216553</v>
+        <v>121216581</v>
       </c>
       <c r="B24" t="n">
-        <v>90705</v>
+        <v>100347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511738</v>
+        <v>511749</v>
       </c>
       <c r="R24" t="n">
-        <v>6733948</v>
+        <v>6733964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216521</v>
+        <v>121216564</v>
       </c>
       <c r="B25" t="n">
-        <v>91127</v>
+        <v>100347</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511691</v>
+        <v>511683</v>
       </c>
       <c r="R25" t="n">
-        <v>6733805</v>
+        <v>6733794</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216531</v>
+        <v>121216512</v>
       </c>
       <c r="B26" t="n">
-        <v>90973</v>
+        <v>90644</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511682</v>
+        <v>511791</v>
       </c>
       <c r="R26" t="n">
-        <v>6733773</v>
+        <v>6733958</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,7 +3198,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3230,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216552</v>
+        <v>121216579</v>
       </c>
       <c r="B27" t="n">
-        <v>90705</v>
+        <v>100347</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3247,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511717</v>
+        <v>511786</v>
       </c>
       <c r="R27" t="n">
-        <v>6733907</v>
+        <v>6733947</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216569</v>
+        <v>121216568</v>
       </c>
       <c r="B28" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3372,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511726</v>
+        <v>511706</v>
       </c>
       <c r="R28" t="n">
-        <v>6733897</v>
+        <v>6733883</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216520</v>
+        <v>121216507</v>
       </c>
       <c r="B29" t="n">
-        <v>91127</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511694</v>
+        <v>511767</v>
       </c>
       <c r="R29" t="n">
-        <v>6733776</v>
+        <v>6733888</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216524</v>
+        <v>121216529</v>
       </c>
       <c r="B30" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3576,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511679</v>
+        <v>511778</v>
       </c>
       <c r="R30" t="n">
-        <v>6733815</v>
+        <v>6733902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,7 +3606,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3638,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216505</v>
+        <v>121216502</v>
       </c>
       <c r="B31" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3678,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511703</v>
+        <v>511691</v>
       </c>
       <c r="R31" t="n">
-        <v>6733823</v>
+        <v>6733814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216547</v>
+        <v>121216535</v>
       </c>
       <c r="B32" t="n">
-        <v>90705</v>
+        <v>90983</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511698</v>
+        <v>511681</v>
       </c>
       <c r="R32" t="n">
-        <v>6733774</v>
+        <v>6733814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,7 +3810,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3842,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216544</v>
+        <v>121216503</v>
       </c>
       <c r="B33" t="n">
-        <v>90701</v>
+        <v>90697</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511752</v>
+        <v>511689</v>
       </c>
       <c r="R33" t="n">
-        <v>6733939</v>
+        <v>6733823</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3918,11 +3923,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216567</v>
+        <v>121216513</v>
       </c>
       <c r="B34" t="n">
-        <v>100337</v>
+        <v>57367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,38 +3961,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511717</v>
+        <v>511726</v>
       </c>
       <c r="R34" t="n">
-        <v>6733840</v>
+        <v>6733944</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216575</v>
+        <v>121216566</v>
       </c>
       <c r="B35" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511726</v>
+        <v>511692</v>
       </c>
       <c r="R35" t="n">
-        <v>6733920</v>
+        <v>6733799</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216533</v>
+        <v>121216580</v>
       </c>
       <c r="B36" t="n">
-        <v>90973</v>
+        <v>100347</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4165,25 +4170,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511683</v>
+        <v>511773</v>
       </c>
       <c r="R36" t="n">
-        <v>6733782</v>
+        <v>6733953</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216573</v>
+        <v>121216575</v>
       </c>
       <c r="B37" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511712</v>
+        <v>511726</v>
       </c>
       <c r="R37" t="n">
-        <v>6733910</v>
+        <v>6733920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4357,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216550</v>
+        <v>121216504</v>
       </c>
       <c r="B38" t="n">
-        <v>90705</v>
+        <v>90697</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,21 +4378,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511697</v>
+        <v>511683</v>
       </c>
       <c r="R38" t="n">
-        <v>6733776</v>
+        <v>6733814</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4427,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4459,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216507</v>
+        <v>121216494</v>
       </c>
       <c r="B39" t="n">
-        <v>90687</v>
+        <v>90662</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,25 +4476,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511767</v>
+        <v>511695</v>
       </c>
       <c r="R39" t="n">
-        <v>6733888</v>
+        <v>6733800</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4524,7 +4529,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4561,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216501</v>
+        <v>121216570</v>
       </c>
       <c r="B40" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4573,25 +4578,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511692</v>
+        <v>511737</v>
       </c>
       <c r="R40" t="n">
-        <v>6733805</v>
+        <v>6733875</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216527</v>
+        <v>121216567</v>
       </c>
       <c r="B41" t="n">
-        <v>91127</v>
+        <v>100347</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511722</v>
+        <v>511717</v>
       </c>
       <c r="R41" t="n">
-        <v>6733823</v>
+        <v>6733840</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4765,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216512</v>
+        <v>121216531</v>
       </c>
       <c r="B42" t="n">
-        <v>90634</v>
+        <v>90983</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4786,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511791</v>
+        <v>511682</v>
       </c>
       <c r="R42" t="n">
-        <v>6733958</v>
+        <v>6733773</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4830,7 +4835,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4867,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216579</v>
+        <v>121216521</v>
       </c>
       <c r="B43" t="n">
-        <v>100337</v>
+        <v>91137</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4879,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511786</v>
+        <v>511691</v>
       </c>
       <c r="R43" t="n">
-        <v>6733947</v>
+        <v>6733805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216513</v>
+        <v>121216526</v>
       </c>
       <c r="B44" t="n">
-        <v>57364</v>
+        <v>91137</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4981,43 +4986,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511726</v>
+        <v>511715</v>
       </c>
       <c r="R44" t="n">
-        <v>6733944</v>
+        <v>6733819</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5076,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216581</v>
+        <v>121216522</v>
       </c>
       <c r="B45" t="n">
-        <v>100337</v>
+        <v>91137</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5088,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511749</v>
+        <v>511691</v>
       </c>
       <c r="R45" t="n">
-        <v>6733964</v>
+        <v>6733814</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216545</v>
+        <v>121216509</v>
       </c>
       <c r="B46" t="n">
-        <v>90701</v>
+        <v>90697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511749</v>
+        <v>511760</v>
       </c>
       <c r="R46" t="n">
-        <v>6733943</v>
+        <v>6733909</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,11 +5254,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5285,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216523</v>
+        <v>121216551</v>
       </c>
       <c r="B47" t="n">
-        <v>91127</v>
+        <v>90715</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,25 +5292,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511689</v>
+        <v>511719</v>
       </c>
       <c r="R47" t="n">
-        <v>6733823</v>
+        <v>6733835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216571</v>
+        <v>121216547</v>
       </c>
       <c r="B48" t="n">
-        <v>100337</v>
+        <v>90715</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511735</v>
+        <v>511698</v>
       </c>
       <c r="R48" t="n">
-        <v>6733890</v>
+        <v>6733774</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,7 +5447,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5489,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216564</v>
+        <v>121216583</v>
       </c>
       <c r="B49" t="n">
-        <v>100337</v>
+        <v>5169</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,34 +5500,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511683</v>
+        <v>511712</v>
       </c>
       <c r="R49" t="n">
-        <v>6733794</v>
+        <v>6733841</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216508</v>
+        <v>121216565</v>
       </c>
       <c r="B50" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5603,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511778</v>
+        <v>511692</v>
       </c>
       <c r="R50" t="n">
-        <v>6733888</v>
+        <v>6733786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216509</v>
+        <v>121216578</v>
       </c>
       <c r="B51" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511760</v>
+        <v>511790</v>
       </c>
       <c r="R51" t="n">
-        <v>6733909</v>
+        <v>6733915</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216519</v>
+        <v>121216527</v>
       </c>
       <c r="B52" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511684</v>
+        <v>511722</v>
       </c>
       <c r="R52" t="n">
-        <v>6733782</v>
+        <v>6733823</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216568</v>
+        <v>121216533</v>
       </c>
       <c r="B53" t="n">
-        <v>100337</v>
+        <v>90983</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511706</v>
+        <v>511683</v>
       </c>
       <c r="R53" t="n">
-        <v>6733883</v>
+        <v>6733782</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216493</v>
+        <v>121216523</v>
       </c>
       <c r="B54" t="n">
-        <v>95618</v>
+        <v>91137</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,25 +6011,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511719</v>
+        <v>511689</v>
       </c>
       <c r="R54" t="n">
-        <v>6733820</v>
+        <v>6733823</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216536</v>
+        <v>121216576</v>
       </c>
       <c r="B55" t="n">
-        <v>90973</v>
+        <v>100347</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,25 +6113,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511766</v>
+        <v>511735</v>
       </c>
       <c r="R55" t="n">
-        <v>6733889</v>
+        <v>6733932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -6206,7 +6206,7 @@
         <v>121216538</v>
       </c>
       <c r="B56" t="n">
-        <v>91760</v>
+        <v>91770</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216525</v>
+        <v>121216559</v>
       </c>
       <c r="B18" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511722</v>
+        <v>511701</v>
       </c>
       <c r="R18" t="n">
-        <v>6733810</v>
+        <v>6733806</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216559</v>
+        <v>121216525</v>
       </c>
       <c r="B19" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511701</v>
+        <v>511722</v>
       </c>
       <c r="R19" t="n">
-        <v>6733806</v>
+        <v>6733810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216503</v>
+        <v>121216566</v>
       </c>
       <c r="B33" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3859,25 +3859,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511689</v>
+        <v>511692</v>
       </c>
       <c r="R33" t="n">
-        <v>6733823</v>
+        <v>6733799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216513</v>
+        <v>121216580</v>
       </c>
       <c r="B34" t="n">
-        <v>57367</v>
+        <v>100347</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,43 +3961,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511726</v>
+        <v>511773</v>
       </c>
       <c r="R34" t="n">
-        <v>6733944</v>
+        <v>6733953</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4056,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216566</v>
+        <v>121216513</v>
       </c>
       <c r="B35" t="n">
-        <v>100347</v>
+        <v>57367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,38 +4063,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511692</v>
+        <v>511726</v>
       </c>
       <c r="R35" t="n">
-        <v>6733799</v>
+        <v>6733944</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216580</v>
+        <v>121216503</v>
       </c>
       <c r="B36" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511773</v>
+        <v>511689</v>
       </c>
       <c r="R36" t="n">
-        <v>6733953</v>
+        <v>6733823</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216570</v>
+        <v>121216531</v>
       </c>
       <c r="B40" t="n">
-        <v>100347</v>
+        <v>90983</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4578,25 +4578,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511737</v>
+        <v>511682</v>
       </c>
       <c r="R40" t="n">
-        <v>6733875</v>
+        <v>6733773</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4668,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216567</v>
+        <v>121216521</v>
       </c>
       <c r="B41" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511717</v>
+        <v>511691</v>
       </c>
       <c r="R41" t="n">
-        <v>6733840</v>
+        <v>6733805</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216531</v>
+        <v>121216570</v>
       </c>
       <c r="B42" t="n">
-        <v>90983</v>
+        <v>100347</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4782,25 +4782,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511682</v>
+        <v>511737</v>
       </c>
       <c r="R42" t="n">
-        <v>6733773</v>
+        <v>6733875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216521</v>
+        <v>121216567</v>
       </c>
       <c r="B43" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511691</v>
+        <v>511717</v>
       </c>
       <c r="R43" t="n">
-        <v>6733805</v>
+        <v>6733840</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216578</v>
+        <v>121216527</v>
       </c>
       <c r="B51" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511790</v>
+        <v>511722</v>
       </c>
       <c r="R51" t="n">
-        <v>6733915</v>
+        <v>6733823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216527</v>
+        <v>121216578</v>
       </c>
       <c r="B52" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511722</v>
+        <v>511790</v>
       </c>
       <c r="R52" t="n">
-        <v>6733823</v>
+        <v>6733915</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216526</v>
+        <v>121216551</v>
       </c>
       <c r="B44" t="n">
-        <v>91137</v>
+        <v>90715</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511715</v>
+        <v>511719</v>
       </c>
       <c r="R44" t="n">
-        <v>6733819</v>
+        <v>6733835</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5076,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216522</v>
+        <v>121216547</v>
       </c>
       <c r="B45" t="n">
-        <v>91137</v>
+        <v>90715</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5088,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511691</v>
+        <v>511698</v>
       </c>
       <c r="R45" t="n">
-        <v>6733814</v>
+        <v>6733774</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216509</v>
+        <v>121216583</v>
       </c>
       <c r="B46" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,38 +5190,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511760</v>
+        <v>511712</v>
       </c>
       <c r="R46" t="n">
-        <v>6733909</v>
+        <v>6733841</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216551</v>
+        <v>121216526</v>
       </c>
       <c r="B47" t="n">
-        <v>90715</v>
+        <v>91137</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5297,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511719</v>
+        <v>511715</v>
       </c>
       <c r="R47" t="n">
-        <v>6733835</v>
+        <v>6733819</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5345,7 +5350,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5382,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216547</v>
+        <v>121216522</v>
       </c>
       <c r="B48" t="n">
-        <v>90715</v>
+        <v>91137</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5394,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511698</v>
+        <v>511691</v>
       </c>
       <c r="R48" t="n">
-        <v>6733774</v>
+        <v>6733814</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5447,7 +5452,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5484,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216583</v>
+        <v>121216509</v>
       </c>
       <c r="B49" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5496,43 +5501,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511712</v>
+        <v>511760</v>
       </c>
       <c r="R49" t="n">
-        <v>6733841</v>
+        <v>6733909</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216508</v>
+        <v>121216495</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511778</v>
+        <v>511704</v>
       </c>
       <c r="R2" t="n">
-        <v>6733888</v>
+        <v>6733869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216577</v>
+        <v>121216547</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511753</v>
+        <v>511698</v>
       </c>
       <c r="R3" t="n">
-        <v>6733916</v>
+        <v>6733774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216536</v>
+        <v>121216504</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511766</v>
+        <v>511683</v>
       </c>
       <c r="R4" t="n">
-        <v>6733889</v>
+        <v>6733814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216501</v>
+        <v>121216505</v>
       </c>
       <c r="B5" t="n">
         <v>90697</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511692</v>
+        <v>511703</v>
       </c>
       <c r="R5" t="n">
-        <v>6733805</v>
+        <v>6733823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216552</v>
+        <v>121216519</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>91137</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511717</v>
+        <v>511684</v>
       </c>
       <c r="R6" t="n">
-        <v>6733907</v>
+        <v>6733782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216520</v>
+        <v>121216568</v>
       </c>
       <c r="B7" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511694</v>
+        <v>511706</v>
       </c>
       <c r="R7" t="n">
-        <v>6733776</v>
+        <v>6733883</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216534</v>
+        <v>121216579</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>100347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511691</v>
+        <v>511786</v>
       </c>
       <c r="R8" t="n">
-        <v>6733814</v>
+        <v>6733947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216519</v>
+        <v>121216536</v>
       </c>
       <c r="B9" t="n">
-        <v>91137</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511684</v>
+        <v>511766</v>
       </c>
       <c r="R9" t="n">
-        <v>6733782</v>
+        <v>6733889</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216495</v>
+        <v>121216544</v>
       </c>
       <c r="B10" t="n">
-        <v>90662</v>
+        <v>90711</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511704</v>
+        <v>511752</v>
       </c>
       <c r="R10" t="n">
-        <v>6733869</v>
+        <v>6733939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216493</v>
+        <v>121216523</v>
       </c>
       <c r="B11" t="n">
-        <v>95628</v>
+        <v>91137</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511719</v>
+        <v>511689</v>
       </c>
       <c r="R11" t="n">
-        <v>6733820</v>
+        <v>6733823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1663,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216571</v>
+        <v>121216501</v>
       </c>
       <c r="B12" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511735</v>
+        <v>511692</v>
       </c>
       <c r="R12" t="n">
-        <v>6733890</v>
+        <v>6733805</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216524</v>
+        <v>121216494</v>
       </c>
       <c r="B13" t="n">
-        <v>91137</v>
+        <v>90662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511679</v>
+        <v>511695</v>
       </c>
       <c r="R13" t="n">
-        <v>6733815</v>
+        <v>6733800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216569</v>
+        <v>121216572</v>
       </c>
       <c r="B14" t="n">
         <v>100347</v>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511726</v>
+        <v>511717</v>
       </c>
       <c r="R14" t="n">
-        <v>6733897</v>
+        <v>6733894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216544</v>
+        <v>121216535</v>
       </c>
       <c r="B15" t="n">
-        <v>90711</v>
+        <v>90983</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511752</v>
+        <v>511681</v>
       </c>
       <c r="R15" t="n">
-        <v>6733939</v>
+        <v>6733814</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,11 +2082,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216553</v>
+        <v>121216529</v>
       </c>
       <c r="B16" t="n">
-        <v>90715</v>
+        <v>91137</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511738</v>
+        <v>511778</v>
       </c>
       <c r="R16" t="n">
-        <v>6733948</v>
+        <v>6733902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216573</v>
+        <v>121216580</v>
       </c>
       <c r="B17" t="n">
         <v>100347</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511712</v>
+        <v>511773</v>
       </c>
       <c r="R17" t="n">
-        <v>6733910</v>
+        <v>6733953</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216559</v>
+        <v>121216567</v>
       </c>
       <c r="B18" t="n">
         <v>100347</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511701</v>
+        <v>511717</v>
       </c>
       <c r="R18" t="n">
-        <v>6733806</v>
+        <v>6733840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216525</v>
+        <v>121216512</v>
       </c>
       <c r="B19" t="n">
-        <v>91137</v>
+        <v>90644</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511722</v>
+        <v>511791</v>
       </c>
       <c r="R19" t="n">
-        <v>6733810</v>
+        <v>6733958</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216505</v>
+        <v>121216569</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511703</v>
+        <v>511726</v>
       </c>
       <c r="R20" t="n">
-        <v>6733823</v>
+        <v>6733897</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216545</v>
+        <v>121216576</v>
       </c>
       <c r="B21" t="n">
-        <v>90711</v>
+        <v>100347</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511749</v>
+        <v>511735</v>
       </c>
       <c r="R21" t="n">
-        <v>6733943</v>
+        <v>6733932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2694,11 +2694,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2725,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216550</v>
+        <v>121216493</v>
       </c>
       <c r="B22" t="n">
-        <v>90715</v>
+        <v>95628</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511697</v>
+        <v>511719</v>
       </c>
       <c r="R22" t="n">
-        <v>6733776</v>
+        <v>6733820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216572</v>
+        <v>121216573</v>
       </c>
       <c r="B23" t="n">
         <v>100347</v>
@@ -2867,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511717</v>
+        <v>511712</v>
       </c>
       <c r="R23" t="n">
-        <v>6733894</v>
+        <v>6733910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2924,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216581</v>
+        <v>121216571</v>
       </c>
       <c r="B24" t="n">
         <v>100347</v>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511749</v>
+        <v>511735</v>
       </c>
       <c r="R24" t="n">
-        <v>6733964</v>
+        <v>6733890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216564</v>
+        <v>121216527</v>
       </c>
       <c r="B25" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511683</v>
+        <v>511722</v>
       </c>
       <c r="R25" t="n">
-        <v>6733794</v>
+        <v>6733823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,7 +3091,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3133,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216512</v>
+        <v>121216508</v>
       </c>
       <c r="B26" t="n">
-        <v>90644</v>
+        <v>90697</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511791</v>
+        <v>511778</v>
       </c>
       <c r="R26" t="n">
-        <v>6733958</v>
+        <v>6733888</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,7 +3193,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3235,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216579</v>
+        <v>121216545</v>
       </c>
       <c r="B27" t="n">
-        <v>100347</v>
+        <v>90711</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511786</v>
+        <v>511749</v>
       </c>
       <c r="R27" t="n">
-        <v>6733947</v>
+        <v>6733943</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3306,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216568</v>
+        <v>121216533</v>
       </c>
       <c r="B28" t="n">
-        <v>100347</v>
+        <v>90983</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511706</v>
+        <v>511683</v>
       </c>
       <c r="R28" t="n">
-        <v>6733883</v>
+        <v>6733782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216507</v>
+        <v>121216559</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511767</v>
+        <v>511701</v>
       </c>
       <c r="R29" t="n">
-        <v>6733888</v>
+        <v>6733806</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216529</v>
+        <v>121216566</v>
       </c>
       <c r="B30" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511778</v>
+        <v>511692</v>
       </c>
       <c r="R30" t="n">
-        <v>6733902</v>
+        <v>6733799</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216502</v>
+        <v>121216578</v>
       </c>
       <c r="B31" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511691</v>
+        <v>511790</v>
       </c>
       <c r="R31" t="n">
-        <v>6733814</v>
+        <v>6733915</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216535</v>
+        <v>121216521</v>
       </c>
       <c r="B32" t="n">
-        <v>90983</v>
+        <v>91137</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511681</v>
+        <v>511691</v>
       </c>
       <c r="R32" t="n">
-        <v>6733814</v>
+        <v>6733805</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216566</v>
+        <v>121216534</v>
       </c>
       <c r="B33" t="n">
-        <v>100347</v>
+        <v>90983</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3859,25 +3859,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511692</v>
+        <v>511691</v>
       </c>
       <c r="R33" t="n">
-        <v>6733799</v>
+        <v>6733814</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216580</v>
+        <v>121216570</v>
       </c>
       <c r="B34" t="n">
         <v>100347</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511773</v>
+        <v>511737</v>
       </c>
       <c r="R34" t="n">
-        <v>6733953</v>
+        <v>6733875</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216513</v>
+        <v>121216564</v>
       </c>
       <c r="B35" t="n">
-        <v>57367</v>
+        <v>100347</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,43 +4063,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511726</v>
+        <v>511683</v>
       </c>
       <c r="R35" t="n">
-        <v>6733944</v>
+        <v>6733794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216503</v>
+        <v>121216507</v>
       </c>
       <c r="B36" t="n">
         <v>90697</v>
@@ -4198,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511689</v>
+        <v>511767</v>
       </c>
       <c r="R36" t="n">
-        <v>6733823</v>
+        <v>6733888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4260,7 +4255,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216575</v>
+        <v>121216565</v>
       </c>
       <c r="B37" t="n">
         <v>100347</v>
@@ -4300,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511726</v>
+        <v>511692</v>
       </c>
       <c r="R37" t="n">
-        <v>6733920</v>
+        <v>6733786</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4362,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216504</v>
+        <v>121216522</v>
       </c>
       <c r="B38" t="n">
-        <v>90697</v>
+        <v>91137</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4374,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,7 +4397,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511683</v>
+        <v>511691</v>
       </c>
       <c r="R38" t="n">
         <v>6733814</v>
@@ -4464,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216494</v>
+        <v>121216502</v>
       </c>
       <c r="B39" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4476,25 +4471,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511695</v>
+        <v>511691</v>
       </c>
       <c r="R39" t="n">
-        <v>6733800</v>
+        <v>6733814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216531</v>
+        <v>121216550</v>
       </c>
       <c r="B40" t="n">
-        <v>90983</v>
+        <v>90715</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511682</v>
+        <v>511697</v>
       </c>
       <c r="R40" t="n">
-        <v>6733773</v>
+        <v>6733776</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216521</v>
+        <v>121216575</v>
       </c>
       <c r="B41" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511691</v>
+        <v>511726</v>
       </c>
       <c r="R41" t="n">
-        <v>6733805</v>
+        <v>6733920</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216570</v>
+        <v>121216525</v>
       </c>
       <c r="B42" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4782,25 +4777,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511737</v>
+        <v>511722</v>
       </c>
       <c r="R42" t="n">
-        <v>6733875</v>
+        <v>6733810</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,7 +4830,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4872,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216567</v>
+        <v>121216513</v>
       </c>
       <c r="B43" t="n">
-        <v>100347</v>
+        <v>57367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,38 +4879,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511717</v>
+        <v>511726</v>
       </c>
       <c r="R43" t="n">
-        <v>6733840</v>
+        <v>6733944</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216551</v>
+        <v>121216583</v>
       </c>
       <c r="B44" t="n">
-        <v>90715</v>
+        <v>5169</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,38 +4986,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511719</v>
+        <v>511712</v>
       </c>
       <c r="R44" t="n">
-        <v>6733835</v>
+        <v>6733841</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216547</v>
+        <v>121216581</v>
       </c>
       <c r="B45" t="n">
-        <v>90715</v>
+        <v>100347</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5093,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511698</v>
+        <v>511749</v>
       </c>
       <c r="R45" t="n">
-        <v>6733774</v>
+        <v>6733964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5141,7 +5146,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5178,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216583</v>
+        <v>121216526</v>
       </c>
       <c r="B46" t="n">
-        <v>5169</v>
+        <v>91137</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,43 +5195,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511712</v>
+        <v>511715</v>
       </c>
       <c r="R46" t="n">
-        <v>6733841</v>
+        <v>6733819</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5285,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216526</v>
+        <v>121216531</v>
       </c>
       <c r="B47" t="n">
-        <v>91137</v>
+        <v>90983</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,25 +5297,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511715</v>
+        <v>511682</v>
       </c>
       <c r="R47" t="n">
-        <v>6733819</v>
+        <v>6733773</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216522</v>
+        <v>121216553</v>
       </c>
       <c r="B48" t="n">
-        <v>91137</v>
+        <v>90715</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511691</v>
+        <v>511738</v>
       </c>
       <c r="R48" t="n">
-        <v>6733814</v>
+        <v>6733948</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216509</v>
+        <v>121216503</v>
       </c>
       <c r="B49" t="n">
         <v>90697</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511760</v>
+        <v>511689</v>
       </c>
       <c r="R49" t="n">
-        <v>6733909</v>
+        <v>6733823</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216565</v>
+        <v>121216552</v>
       </c>
       <c r="B50" t="n">
-        <v>100347</v>
+        <v>90715</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5603,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511692</v>
+        <v>511717</v>
       </c>
       <c r="R50" t="n">
-        <v>6733786</v>
+        <v>6733907</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216527</v>
+        <v>121216551</v>
       </c>
       <c r="B51" t="n">
-        <v>91137</v>
+        <v>90715</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511722</v>
+        <v>511719</v>
       </c>
       <c r="R51" t="n">
-        <v>6733823</v>
+        <v>6733835</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5795,7 +5795,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216578</v>
+        <v>121216577</v>
       </c>
       <c r="B52" t="n">
         <v>100347</v>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511790</v>
+        <v>511753</v>
       </c>
       <c r="R52" t="n">
-        <v>6733915</v>
+        <v>6733916</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216533</v>
+        <v>121216520</v>
       </c>
       <c r="B53" t="n">
-        <v>90983</v>
+        <v>91137</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511683</v>
+        <v>511694</v>
       </c>
       <c r="R53" t="n">
-        <v>6733782</v>
+        <v>6733776</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216523</v>
+        <v>121216509</v>
       </c>
       <c r="B54" t="n">
-        <v>91137</v>
+        <v>90697</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,25 +6011,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511689</v>
+        <v>511760</v>
       </c>
       <c r="R54" t="n">
-        <v>6733823</v>
+        <v>6733909</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216576</v>
+        <v>121216524</v>
       </c>
       <c r="B55" t="n">
-        <v>100347</v>
+        <v>91137</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,25 +6113,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511735</v>
+        <v>511679</v>
       </c>
       <c r="R55" t="n">
-        <v>6733932</v>
+        <v>6733815</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216536</v>
+        <v>121216544</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>90711</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511766</v>
+        <v>511752</v>
       </c>
       <c r="R9" t="n">
-        <v>6733889</v>
+        <v>6733939</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1465,6 +1465,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216544</v>
+        <v>121216536</v>
       </c>
       <c r="B10" t="n">
-        <v>90711</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511752</v>
+        <v>511766</v>
       </c>
       <c r="R10" t="n">
-        <v>6733939</v>
+        <v>6733889</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1561,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4765,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216525</v>
+        <v>121216513</v>
       </c>
       <c r="B42" t="n">
-        <v>91137</v>
+        <v>57367</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4777,38 +4777,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511722</v>
+        <v>511726</v>
       </c>
       <c r="R42" t="n">
-        <v>6733810</v>
+        <v>6733944</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4830,7 +4835,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4867,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216513</v>
+        <v>121216581</v>
       </c>
       <c r="B43" t="n">
-        <v>57367</v>
+        <v>100347</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4879,43 +4884,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511726</v>
+        <v>511749</v>
       </c>
       <c r="R43" t="n">
-        <v>6733944</v>
+        <v>6733964</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216583</v>
+        <v>121216525</v>
       </c>
       <c r="B44" t="n">
-        <v>5169</v>
+        <v>91137</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,43 +4986,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511712</v>
+        <v>511722</v>
       </c>
       <c r="R44" t="n">
-        <v>6733841</v>
+        <v>6733810</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5044,7 +5039,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216581</v>
+        <v>121216583</v>
       </c>
       <c r="B45" t="n">
-        <v>100347</v>
+        <v>5169</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,34 +5092,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511749</v>
+        <v>511712</v>
       </c>
       <c r="R45" t="n">
-        <v>6733964</v>
+        <v>6733841</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216495</v>
+        <v>121216583</v>
       </c>
       <c r="B2" t="n">
-        <v>90662</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511704</v>
+        <v>511712</v>
       </c>
       <c r="R2" t="n">
-        <v>6733869</v>
+        <v>6733841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216547</v>
+        <v>121216566</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>100360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511698</v>
+        <v>511692</v>
       </c>
       <c r="R3" t="n">
-        <v>6733774</v>
+        <v>6733799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +847,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216504</v>
+        <v>121216551</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>90727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511683</v>
+        <v>511719</v>
       </c>
       <c r="R4" t="n">
-        <v>6733814</v>
+        <v>6733835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216505</v>
+        <v>121216570</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511703</v>
+        <v>511737</v>
       </c>
       <c r="R5" t="n">
-        <v>6733823</v>
+        <v>6733875</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216519</v>
+        <v>121216571</v>
       </c>
       <c r="B6" t="n">
-        <v>91137</v>
+        <v>100360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511684</v>
+        <v>511735</v>
       </c>
       <c r="R6" t="n">
-        <v>6733782</v>
+        <v>6733890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216568</v>
+        <v>121216564</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511706</v>
+        <v>511683</v>
       </c>
       <c r="R7" t="n">
-        <v>6733883</v>
+        <v>6733794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216579</v>
+        <v>121216504</v>
       </c>
       <c r="B8" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511786</v>
+        <v>511683</v>
       </c>
       <c r="R8" t="n">
-        <v>6733947</v>
+        <v>6733814</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216544</v>
+        <v>121216502</v>
       </c>
       <c r="B9" t="n">
-        <v>90711</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511752</v>
+        <v>511691</v>
       </c>
       <c r="R9" t="n">
-        <v>6733939</v>
+        <v>6733814</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216536</v>
+        <v>121216580</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>100360</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511766</v>
+        <v>511773</v>
       </c>
       <c r="R10" t="n">
-        <v>6733889</v>
+        <v>6733953</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216523</v>
+        <v>121216512</v>
       </c>
       <c r="B11" t="n">
-        <v>91137</v>
+        <v>90656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511689</v>
+        <v>511791</v>
       </c>
       <c r="R11" t="n">
-        <v>6733823</v>
+        <v>6733958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216501</v>
+        <v>121216575</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511692</v>
+        <v>511726</v>
       </c>
       <c r="R12" t="n">
-        <v>6733805</v>
+        <v>6733920</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216494</v>
+        <v>121216547</v>
       </c>
       <c r="B13" t="n">
-        <v>90662</v>
+        <v>90727</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511695</v>
+        <v>511698</v>
       </c>
       <c r="R13" t="n">
-        <v>6733800</v>
+        <v>6733774</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216572</v>
+        <v>121216509</v>
       </c>
       <c r="B14" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511717</v>
+        <v>511760</v>
       </c>
       <c r="R14" t="n">
-        <v>6733894</v>
+        <v>6733909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216535</v>
+        <v>121216578</v>
       </c>
       <c r="B15" t="n">
-        <v>90983</v>
+        <v>100360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511681</v>
+        <v>511790</v>
       </c>
       <c r="R15" t="n">
-        <v>6733814</v>
+        <v>6733915</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216529</v>
+        <v>121216523</v>
       </c>
       <c r="B16" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511778</v>
+        <v>511689</v>
       </c>
       <c r="R16" t="n">
-        <v>6733902</v>
+        <v>6733823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216580</v>
+        <v>121216508</v>
       </c>
       <c r="B17" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511773</v>
+        <v>511778</v>
       </c>
       <c r="R17" t="n">
-        <v>6733953</v>
+        <v>6733888</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216567</v>
+        <v>121216524</v>
       </c>
       <c r="B18" t="n">
-        <v>100347</v>
+        <v>91149</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511717</v>
+        <v>511679</v>
       </c>
       <c r="R18" t="n">
-        <v>6733840</v>
+        <v>6733815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216512</v>
+        <v>121216550</v>
       </c>
       <c r="B19" t="n">
-        <v>90644</v>
+        <v>90727</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511791</v>
+        <v>511697</v>
       </c>
       <c r="R19" t="n">
-        <v>6733958</v>
+        <v>6733776</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216569</v>
+        <v>121216579</v>
       </c>
       <c r="B20" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511726</v>
+        <v>511786</v>
       </c>
       <c r="R20" t="n">
-        <v>6733897</v>
+        <v>6733947</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216576</v>
+        <v>121216520</v>
       </c>
       <c r="B21" t="n">
-        <v>100347</v>
+        <v>91149</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511735</v>
+        <v>511694</v>
       </c>
       <c r="R21" t="n">
-        <v>6733932</v>
+        <v>6733776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216493</v>
+        <v>121216535</v>
       </c>
       <c r="B22" t="n">
-        <v>95628</v>
+        <v>90995</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511719</v>
+        <v>511681</v>
       </c>
       <c r="R22" t="n">
-        <v>6733820</v>
+        <v>6733814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216573</v>
+        <v>121216527</v>
       </c>
       <c r="B23" t="n">
-        <v>100347</v>
+        <v>91149</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511712</v>
+        <v>511722</v>
       </c>
       <c r="R23" t="n">
-        <v>6733910</v>
+        <v>6733823</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216571</v>
+        <v>121216521</v>
       </c>
       <c r="B24" t="n">
-        <v>100347</v>
+        <v>91149</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511735</v>
+        <v>511691</v>
       </c>
       <c r="R24" t="n">
-        <v>6733890</v>
+        <v>6733805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216527</v>
+        <v>121216495</v>
       </c>
       <c r="B25" t="n">
-        <v>91137</v>
+        <v>90674</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511722</v>
+        <v>511704</v>
       </c>
       <c r="R25" t="n">
-        <v>6733823</v>
+        <v>6733869</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216508</v>
+        <v>121216559</v>
       </c>
       <c r="B26" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511778</v>
+        <v>511701</v>
       </c>
       <c r="R26" t="n">
-        <v>6733888</v>
+        <v>6733806</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216545</v>
+        <v>121216525</v>
       </c>
       <c r="B27" t="n">
-        <v>90711</v>
+        <v>91149</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511749</v>
+        <v>511722</v>
       </c>
       <c r="R27" t="n">
-        <v>6733943</v>
+        <v>6733810</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3306,11 +3306,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216533</v>
+        <v>121216519</v>
       </c>
       <c r="B28" t="n">
-        <v>90983</v>
+        <v>91149</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,7 +3372,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511683</v>
+        <v>511684</v>
       </c>
       <c r="R28" t="n">
         <v>6733782</v>
@@ -3439,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216559</v>
+        <v>121216576</v>
       </c>
       <c r="B29" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511701</v>
+        <v>511735</v>
       </c>
       <c r="R29" t="n">
-        <v>6733806</v>
+        <v>6733932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216566</v>
+        <v>121216533</v>
       </c>
       <c r="B30" t="n">
-        <v>100347</v>
+        <v>90995</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511692</v>
+        <v>511683</v>
       </c>
       <c r="R30" t="n">
-        <v>6733799</v>
+        <v>6733782</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216578</v>
+        <v>121216553</v>
       </c>
       <c r="B31" t="n">
-        <v>100347</v>
+        <v>90727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3650,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511790</v>
+        <v>511738</v>
       </c>
       <c r="R31" t="n">
-        <v>6733915</v>
+        <v>6733948</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,7 +3703,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3745,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216521</v>
+        <v>121216526</v>
       </c>
       <c r="B32" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511691</v>
+        <v>511715</v>
       </c>
       <c r="R32" t="n">
-        <v>6733805</v>
+        <v>6733819</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,7 +3805,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3847,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216534</v>
+        <v>121216565</v>
       </c>
       <c r="B33" t="n">
-        <v>90983</v>
+        <v>100360</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3859,25 +3854,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511691</v>
+        <v>511692</v>
       </c>
       <c r="R33" t="n">
-        <v>6733814</v>
+        <v>6733786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,7 +3907,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3949,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216570</v>
+        <v>121216501</v>
       </c>
       <c r="B34" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,25 +3956,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511737</v>
+        <v>511692</v>
       </c>
       <c r="R34" t="n">
-        <v>6733875</v>
+        <v>6733805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216564</v>
+        <v>121216545</v>
       </c>
       <c r="B35" t="n">
-        <v>100347</v>
+        <v>90723</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,25 +4058,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511683</v>
+        <v>511749</v>
       </c>
       <c r="R35" t="n">
-        <v>6733794</v>
+        <v>6733943</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4127,6 +4122,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216507</v>
+        <v>121216581</v>
       </c>
       <c r="B36" t="n">
-        <v>90697</v>
+        <v>100360</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511767</v>
+        <v>511749</v>
       </c>
       <c r="R36" t="n">
-        <v>6733888</v>
+        <v>6733964</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216565</v>
+        <v>121216513</v>
       </c>
       <c r="B37" t="n">
-        <v>100347</v>
+        <v>57367</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,38 +4267,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511692</v>
+        <v>511726</v>
       </c>
       <c r="R37" t="n">
-        <v>6733786</v>
+        <v>6733944</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216522</v>
+        <v>121216536</v>
       </c>
       <c r="B38" t="n">
-        <v>91137</v>
+        <v>90995</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,25 +4374,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511691</v>
+        <v>511766</v>
       </c>
       <c r="R38" t="n">
-        <v>6733814</v>
+        <v>6733889</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4427,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4459,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216502</v>
+        <v>121216522</v>
       </c>
       <c r="B39" t="n">
-        <v>90697</v>
+        <v>91149</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,25 +4476,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4561,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216550</v>
+        <v>121216493</v>
       </c>
       <c r="B40" t="n">
-        <v>90715</v>
+        <v>95641</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511697</v>
+        <v>511719</v>
       </c>
       <c r="R40" t="n">
-        <v>6733776</v>
+        <v>6733820</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216575</v>
+        <v>121216507</v>
       </c>
       <c r="B41" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511726</v>
+        <v>511767</v>
       </c>
       <c r="R41" t="n">
-        <v>6733920</v>
+        <v>6733888</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,7 +4733,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4765,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216513</v>
+        <v>121216567</v>
       </c>
       <c r="B42" t="n">
-        <v>57367</v>
+        <v>100360</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4777,43 +4782,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511726</v>
+        <v>511717</v>
       </c>
       <c r="R42" t="n">
-        <v>6733944</v>
+        <v>6733840</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216581</v>
+        <v>121216573</v>
       </c>
       <c r="B43" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511749</v>
+        <v>511712</v>
       </c>
       <c r="R43" t="n">
-        <v>6733964</v>
+        <v>6733910</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216525</v>
+        <v>121216577</v>
       </c>
       <c r="B44" t="n">
-        <v>91137</v>
+        <v>100360</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511722</v>
+        <v>511753</v>
       </c>
       <c r="R44" t="n">
-        <v>6733810</v>
+        <v>6733916</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5076,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216583</v>
+        <v>121216494</v>
       </c>
       <c r="B45" t="n">
-        <v>5169</v>
+        <v>90674</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5092,39 +5092,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511712</v>
+        <v>511695</v>
       </c>
       <c r="R45" t="n">
-        <v>6733841</v>
+        <v>6733800</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216526</v>
+        <v>121216572</v>
       </c>
       <c r="B46" t="n">
-        <v>91137</v>
+        <v>100360</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5195,25 +5190,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511715</v>
+        <v>511717</v>
       </c>
       <c r="R46" t="n">
-        <v>6733819</v>
+        <v>6733894</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5285,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216531</v>
+        <v>121216569</v>
       </c>
       <c r="B47" t="n">
-        <v>90983</v>
+        <v>100360</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,25 +5292,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511682</v>
+        <v>511726</v>
       </c>
       <c r="R47" t="n">
-        <v>6733773</v>
+        <v>6733897</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5350,7 +5345,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5387,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216553</v>
+        <v>121216568</v>
       </c>
       <c r="B48" t="n">
-        <v>90715</v>
+        <v>100360</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511738</v>
+        <v>511706</v>
       </c>
       <c r="R48" t="n">
-        <v>6733948</v>
+        <v>6733883</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216503</v>
+        <v>121216544</v>
       </c>
       <c r="B49" t="n">
-        <v>90697</v>
+        <v>90723</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5500,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511689</v>
+        <v>511752</v>
       </c>
       <c r="R49" t="n">
-        <v>6733823</v>
+        <v>6733939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,6 +5560,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216552</v>
+        <v>121216529</v>
       </c>
       <c r="B50" t="n">
-        <v>90715</v>
+        <v>91149</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5603,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511717</v>
+        <v>511778</v>
       </c>
       <c r="R50" t="n">
-        <v>6733907</v>
+        <v>6733902</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216551</v>
+        <v>121216503</v>
       </c>
       <c r="B51" t="n">
-        <v>90715</v>
+        <v>90709</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511719</v>
+        <v>511689</v>
       </c>
       <c r="R51" t="n">
-        <v>6733835</v>
+        <v>6733823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216577</v>
+        <v>121216505</v>
       </c>
       <c r="B52" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511753</v>
+        <v>511703</v>
       </c>
       <c r="R52" t="n">
-        <v>6733916</v>
+        <v>6733823</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216520</v>
+        <v>121216534</v>
       </c>
       <c r="B53" t="n">
-        <v>91137</v>
+        <v>90995</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511694</v>
+        <v>511691</v>
       </c>
       <c r="R53" t="n">
-        <v>6733776</v>
+        <v>6733814</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216509</v>
+        <v>121216531</v>
       </c>
       <c r="B54" t="n">
-        <v>90697</v>
+        <v>90995</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511760</v>
+        <v>511682</v>
       </c>
       <c r="R54" t="n">
-        <v>6733909</v>
+        <v>6733773</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216524</v>
+        <v>121216552</v>
       </c>
       <c r="B55" t="n">
-        <v>91137</v>
+        <v>90727</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,25 +6113,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511679</v>
+        <v>511717</v>
       </c>
       <c r="R55" t="n">
-        <v>6733815</v>
+        <v>6733907</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
         <v>121216538</v>
       </c>
       <c r="B56" t="n">
-        <v>91770</v>
+        <v>91782</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216583</v>
+        <v>121216536</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>90996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511712</v>
+        <v>511766</v>
       </c>
       <c r="R2" t="n">
-        <v>6733841</v>
+        <v>6733889</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216566</v>
+        <v>121216564</v>
       </c>
       <c r="B3" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511692</v>
+        <v>511683</v>
       </c>
       <c r="R3" t="n">
-        <v>6733799</v>
+        <v>6733794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216551</v>
+        <v>121216579</v>
       </c>
       <c r="B4" t="n">
-        <v>90727</v>
+        <v>100361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511719</v>
+        <v>511786</v>
       </c>
       <c r="R4" t="n">
-        <v>6733835</v>
+        <v>6733947</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216570</v>
+        <v>121216568</v>
       </c>
       <c r="B5" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511737</v>
+        <v>511706</v>
       </c>
       <c r="R5" t="n">
-        <v>6733875</v>
+        <v>6733883</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216571</v>
+        <v>121216493</v>
       </c>
       <c r="B6" t="n">
-        <v>100360</v>
+        <v>95642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511735</v>
+        <v>511719</v>
       </c>
       <c r="R6" t="n">
-        <v>6733890</v>
+        <v>6733820</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1148,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216564</v>
+        <v>121216504</v>
       </c>
       <c r="B7" t="n">
-        <v>100360</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,7 +1228,7 @@
         <v>511683</v>
       </c>
       <c r="R7" t="n">
-        <v>6733794</v>
+        <v>6733814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216504</v>
+        <v>121216522</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,7 +1327,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511683</v>
+        <v>511691</v>
       </c>
       <c r="R8" t="n">
         <v>6733814</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216502</v>
+        <v>121216505</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511691</v>
+        <v>511703</v>
       </c>
       <c r="R9" t="n">
-        <v>6733814</v>
+        <v>6733823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216580</v>
+        <v>121216521</v>
       </c>
       <c r="B10" t="n">
-        <v>100360</v>
+        <v>91150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511773</v>
+        <v>511691</v>
       </c>
       <c r="R10" t="n">
-        <v>6733953</v>
+        <v>6733805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216512</v>
+        <v>121216567</v>
       </c>
       <c r="B11" t="n">
-        <v>90656</v>
+        <v>100361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511791</v>
+        <v>511717</v>
       </c>
       <c r="R11" t="n">
-        <v>6733958</v>
+        <v>6733840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216575</v>
+        <v>121216526</v>
       </c>
       <c r="B12" t="n">
-        <v>100360</v>
+        <v>91150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511726</v>
+        <v>511715</v>
       </c>
       <c r="R12" t="n">
-        <v>6733920</v>
+        <v>6733819</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,7 +1760,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216547</v>
+        <v>121216569</v>
       </c>
       <c r="B13" t="n">
-        <v>90727</v>
+        <v>100361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511698</v>
+        <v>511726</v>
       </c>
       <c r="R13" t="n">
-        <v>6733774</v>
+        <v>6733897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216509</v>
+        <v>121216512</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>90657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511760</v>
+        <v>511791</v>
       </c>
       <c r="R14" t="n">
-        <v>6733909</v>
+        <v>6733958</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216578</v>
+        <v>121216551</v>
       </c>
       <c r="B15" t="n">
-        <v>100360</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511790</v>
+        <v>511719</v>
       </c>
       <c r="R15" t="n">
-        <v>6733915</v>
+        <v>6733835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2066,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216523</v>
+        <v>121216527</v>
       </c>
       <c r="B16" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,7 +2143,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511689</v>
+        <v>511722</v>
       </c>
       <c r="R16" t="n">
         <v>6733823</v>
@@ -2173,7 +2168,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216508</v>
+        <v>121216523</v>
       </c>
       <c r="B17" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511778</v>
+        <v>511689</v>
       </c>
       <c r="R17" t="n">
-        <v>6733888</v>
+        <v>6733823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,7 +2270,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216524</v>
+        <v>121216529</v>
       </c>
       <c r="B18" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511679</v>
+        <v>511778</v>
       </c>
       <c r="R18" t="n">
-        <v>6733815</v>
+        <v>6733902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216550</v>
+        <v>121216525</v>
       </c>
       <c r="B19" t="n">
-        <v>90727</v>
+        <v>91150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511697</v>
+        <v>511722</v>
       </c>
       <c r="R19" t="n">
-        <v>6733776</v>
+        <v>6733810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216579</v>
+        <v>121216578</v>
       </c>
       <c r="B20" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511786</v>
+        <v>511790</v>
       </c>
       <c r="R20" t="n">
-        <v>6733947</v>
+        <v>6733915</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2576,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2618,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216520</v>
+        <v>121216503</v>
       </c>
       <c r="B21" t="n">
-        <v>91149</v>
+        <v>90710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511694</v>
+        <v>511689</v>
       </c>
       <c r="R21" t="n">
-        <v>6733776</v>
+        <v>6733823</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2678,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2720,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216535</v>
+        <v>121216547</v>
       </c>
       <c r="B22" t="n">
-        <v>90995</v>
+        <v>90728</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511681</v>
+        <v>511698</v>
       </c>
       <c r="R22" t="n">
-        <v>6733814</v>
+        <v>6733774</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2822,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216527</v>
+        <v>121216573</v>
       </c>
       <c r="B23" t="n">
-        <v>91149</v>
+        <v>100361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511722</v>
+        <v>511712</v>
       </c>
       <c r="R23" t="n">
-        <v>6733823</v>
+        <v>6733910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2882,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2924,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216521</v>
+        <v>121216572</v>
       </c>
       <c r="B24" t="n">
-        <v>91149</v>
+        <v>100361</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511691</v>
+        <v>511717</v>
       </c>
       <c r="R24" t="n">
-        <v>6733805</v>
+        <v>6733894</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216495</v>
+        <v>121216535</v>
       </c>
       <c r="B25" t="n">
-        <v>90674</v>
+        <v>90996</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511704</v>
+        <v>511681</v>
       </c>
       <c r="R25" t="n">
-        <v>6733869</v>
+        <v>6733814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216559</v>
+        <v>121216550</v>
       </c>
       <c r="B26" t="n">
-        <v>100360</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511701</v>
+        <v>511697</v>
       </c>
       <c r="R26" t="n">
-        <v>6733806</v>
+        <v>6733776</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,7 +3188,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3230,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216525</v>
+        <v>121216583</v>
       </c>
       <c r="B27" t="n">
-        <v>91149</v>
+        <v>5169</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,38 +3237,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511722</v>
+        <v>511712</v>
       </c>
       <c r="R27" t="n">
-        <v>6733810</v>
+        <v>6733841</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216519</v>
+        <v>121216577</v>
       </c>
       <c r="B28" t="n">
-        <v>91149</v>
+        <v>100361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511684</v>
+        <v>511753</v>
       </c>
       <c r="R28" t="n">
-        <v>6733782</v>
+        <v>6733916</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216576</v>
+        <v>121216575</v>
       </c>
       <c r="B29" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511735</v>
+        <v>511726</v>
       </c>
       <c r="R29" t="n">
-        <v>6733932</v>
+        <v>6733920</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216533</v>
+        <v>121216580</v>
       </c>
       <c r="B30" t="n">
-        <v>90995</v>
+        <v>100361</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511683</v>
+        <v>511773</v>
       </c>
       <c r="R30" t="n">
-        <v>6733782</v>
+        <v>6733953</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216553</v>
+        <v>121216501</v>
       </c>
       <c r="B31" t="n">
-        <v>90727</v>
+        <v>90710</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511738</v>
+        <v>511692</v>
       </c>
       <c r="R31" t="n">
-        <v>6733948</v>
+        <v>6733805</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216526</v>
+        <v>121216545</v>
       </c>
       <c r="B32" t="n">
-        <v>91149</v>
+        <v>90724</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511715</v>
+        <v>511749</v>
       </c>
       <c r="R32" t="n">
-        <v>6733819</v>
+        <v>6733943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3816,6 +3816,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3842,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216565</v>
+        <v>121216502</v>
       </c>
       <c r="B33" t="n">
-        <v>100360</v>
+        <v>90710</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3854,25 +3859,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511692</v>
+        <v>511691</v>
       </c>
       <c r="R33" t="n">
-        <v>6733786</v>
+        <v>6733814</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,7 +3912,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3944,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216501</v>
+        <v>121216531</v>
       </c>
       <c r="B34" t="n">
-        <v>90709</v>
+        <v>90996</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511692</v>
+        <v>511682</v>
       </c>
       <c r="R34" t="n">
-        <v>6733805</v>
+        <v>6733773</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,7 +4014,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4046,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216545</v>
+        <v>121216495</v>
       </c>
       <c r="B35" t="n">
-        <v>90723</v>
+        <v>90675</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4058,25 +4063,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511749</v>
+        <v>511704</v>
       </c>
       <c r="R35" t="n">
-        <v>6733943</v>
+        <v>6733869</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4122,11 +4127,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216581</v>
+        <v>121216570</v>
       </c>
       <c r="B36" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511749</v>
+        <v>511737</v>
       </c>
       <c r="R36" t="n">
-        <v>6733964</v>
+        <v>6733875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216513</v>
+        <v>121216581</v>
       </c>
       <c r="B37" t="n">
-        <v>57367</v>
+        <v>100361</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,43 +4267,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511726</v>
+        <v>511749</v>
       </c>
       <c r="R37" t="n">
-        <v>6733944</v>
+        <v>6733964</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4362,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216536</v>
+        <v>121216571</v>
       </c>
       <c r="B38" t="n">
-        <v>90995</v>
+        <v>100361</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4374,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511766</v>
+        <v>511735</v>
       </c>
       <c r="R38" t="n">
-        <v>6733889</v>
+        <v>6733890</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4427,7 +4422,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4464,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216522</v>
+        <v>121216519</v>
       </c>
       <c r="B39" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511691</v>
+        <v>511684</v>
       </c>
       <c r="R39" t="n">
-        <v>6733814</v>
+        <v>6733782</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216493</v>
+        <v>121216552</v>
       </c>
       <c r="B40" t="n">
-        <v>95641</v>
+        <v>90728</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,21 +4577,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511719</v>
+        <v>511717</v>
       </c>
       <c r="R40" t="n">
-        <v>6733820</v>
+        <v>6733907</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,7 +4626,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4668,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216507</v>
+        <v>121216520</v>
       </c>
       <c r="B41" t="n">
-        <v>90709</v>
+        <v>91150</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511767</v>
+        <v>511694</v>
       </c>
       <c r="R41" t="n">
-        <v>6733888</v>
+        <v>6733776</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216567</v>
+        <v>121216544</v>
       </c>
       <c r="B42" t="n">
-        <v>100360</v>
+        <v>90724</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4782,25 +4777,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511717</v>
+        <v>511752</v>
       </c>
       <c r="R42" t="n">
-        <v>6733840</v>
+        <v>6733939</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4846,6 +4841,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216573</v>
+        <v>121216524</v>
       </c>
       <c r="B43" t="n">
-        <v>100360</v>
+        <v>91150</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511712</v>
+        <v>511679</v>
       </c>
       <c r="R43" t="n">
-        <v>6733910</v>
+        <v>6733815</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216577</v>
+        <v>121216553</v>
       </c>
       <c r="B44" t="n">
-        <v>100360</v>
+        <v>90728</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511753</v>
+        <v>511738</v>
       </c>
       <c r="R44" t="n">
-        <v>6733916</v>
+        <v>6733948</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216494</v>
+        <v>121216565</v>
       </c>
       <c r="B45" t="n">
-        <v>90674</v>
+        <v>100361</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511695</v>
+        <v>511692</v>
       </c>
       <c r="R45" t="n">
-        <v>6733800</v>
+        <v>6733786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216572</v>
+        <v>121216507</v>
       </c>
       <c r="B46" t="n">
-        <v>100360</v>
+        <v>90710</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,25 +5190,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511717</v>
+        <v>511767</v>
       </c>
       <c r="R46" t="n">
-        <v>6733894</v>
+        <v>6733888</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216569</v>
+        <v>121216534</v>
       </c>
       <c r="B47" t="n">
-        <v>100360</v>
+        <v>90996</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5292,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511726</v>
+        <v>511691</v>
       </c>
       <c r="R47" t="n">
-        <v>6733897</v>
+        <v>6733814</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5382,10 +5382,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216568</v>
+        <v>121216494</v>
       </c>
       <c r="B48" t="n">
-        <v>100360</v>
+        <v>90675</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511706</v>
+        <v>511695</v>
       </c>
       <c r="R48" t="n">
-        <v>6733883</v>
+        <v>6733800</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216544</v>
+        <v>121216576</v>
       </c>
       <c r="B49" t="n">
-        <v>90723</v>
+        <v>100361</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5496,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511752</v>
+        <v>511735</v>
       </c>
       <c r="R49" t="n">
-        <v>6733939</v>
+        <v>6733932</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5560,11 +5560,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5591,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216529</v>
+        <v>121216559</v>
       </c>
       <c r="B50" t="n">
-        <v>91149</v>
+        <v>100361</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5598,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511778</v>
+        <v>511701</v>
       </c>
       <c r="R50" t="n">
-        <v>6733902</v>
+        <v>6733806</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5651,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216503</v>
+        <v>121216533</v>
       </c>
       <c r="B51" t="n">
-        <v>90709</v>
+        <v>90996</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5704,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511689</v>
+        <v>511683</v>
       </c>
       <c r="R51" t="n">
-        <v>6733823</v>
+        <v>6733782</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216505</v>
+        <v>121216508</v>
       </c>
       <c r="B52" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5835,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511703</v>
+        <v>511778</v>
       </c>
       <c r="R52" t="n">
-        <v>6733823</v>
+        <v>6733888</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5860,7 +5855,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5897,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216534</v>
+        <v>121216566</v>
       </c>
       <c r="B53" t="n">
-        <v>90995</v>
+        <v>100361</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511691</v>
+        <v>511692</v>
       </c>
       <c r="R53" t="n">
-        <v>6733814</v>
+        <v>6733799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216531</v>
+        <v>121216509</v>
       </c>
       <c r="B54" t="n">
-        <v>90995</v>
+        <v>90710</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511682</v>
+        <v>511760</v>
       </c>
       <c r="R54" t="n">
-        <v>6733773</v>
+        <v>6733909</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6064,7 +6059,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -6101,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216552</v>
+        <v>121216513</v>
       </c>
       <c r="B55" t="n">
-        <v>90727</v>
+        <v>57367</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6117,34 +6112,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511717</v>
+        <v>511726</v>
       </c>
       <c r="R55" t="n">
-        <v>6733907</v>
+        <v>6733944</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
         <v>121216538</v>
       </c>
       <c r="B56" t="n">
-        <v>91782</v>
+        <v>91783</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216536</v>
+        <v>121216580</v>
       </c>
       <c r="B2" t="n">
-        <v>90996</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511766</v>
+        <v>511773</v>
       </c>
       <c r="R2" t="n">
-        <v>6733889</v>
+        <v>6733953</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216564</v>
+        <v>121216568</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511683</v>
+        <v>511706</v>
       </c>
       <c r="R3" t="n">
-        <v>6733794</v>
+        <v>6733883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216579</v>
+        <v>121216551</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511786</v>
+        <v>511719</v>
       </c>
       <c r="R4" t="n">
-        <v>6733947</v>
+        <v>6733835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216568</v>
+        <v>121216552</v>
       </c>
       <c r="B5" t="n">
-        <v>100361</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511706</v>
+        <v>511717</v>
       </c>
       <c r="R5" t="n">
-        <v>6733883</v>
+        <v>6733907</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216493</v>
+        <v>121216508</v>
       </c>
       <c r="B6" t="n">
-        <v>95642</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511719</v>
+        <v>511778</v>
       </c>
       <c r="R6" t="n">
-        <v>6733820</v>
+        <v>6733888</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216504</v>
+        <v>121216501</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511683</v>
+        <v>511692</v>
       </c>
       <c r="R7" t="n">
-        <v>6733814</v>
+        <v>6733805</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216522</v>
+        <v>121216524</v>
       </c>
       <c r="B8" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511691</v>
+        <v>511679</v>
       </c>
       <c r="R8" t="n">
-        <v>6733814</v>
+        <v>6733815</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216505</v>
+        <v>121216531</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511703</v>
+        <v>511682</v>
       </c>
       <c r="R9" t="n">
-        <v>6733823</v>
+        <v>6733773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216521</v>
+        <v>121216567</v>
       </c>
       <c r="B10" t="n">
-        <v>91150</v>
+        <v>100364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511691</v>
+        <v>511717</v>
       </c>
       <c r="R10" t="n">
-        <v>6733805</v>
+        <v>6733840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216567</v>
+        <v>121216544</v>
       </c>
       <c r="B11" t="n">
-        <v>100361</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511717</v>
+        <v>511752</v>
       </c>
       <c r="R11" t="n">
-        <v>6733840</v>
+        <v>6733939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216526</v>
+        <v>121216523</v>
       </c>
       <c r="B12" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511715</v>
+        <v>511689</v>
       </c>
       <c r="R12" t="n">
-        <v>6733819</v>
+        <v>6733823</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1765,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216569</v>
+        <v>121216526</v>
       </c>
       <c r="B13" t="n">
-        <v>100361</v>
+        <v>91153</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511726</v>
+        <v>511715</v>
       </c>
       <c r="R13" t="n">
-        <v>6733897</v>
+        <v>6733819</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216512</v>
+        <v>121216576</v>
       </c>
       <c r="B14" t="n">
-        <v>90657</v>
+        <v>100364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511791</v>
+        <v>511735</v>
       </c>
       <c r="R14" t="n">
-        <v>6733958</v>
+        <v>6733932</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216551</v>
+        <v>121216512</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>90660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511719</v>
+        <v>511791</v>
       </c>
       <c r="R15" t="n">
-        <v>6733835</v>
+        <v>6733958</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216527</v>
+        <v>121216502</v>
       </c>
       <c r="B16" t="n">
-        <v>91150</v>
+        <v>90713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511722</v>
+        <v>511691</v>
       </c>
       <c r="R16" t="n">
-        <v>6733823</v>
+        <v>6733814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2173,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216523</v>
+        <v>121216578</v>
       </c>
       <c r="B17" t="n">
-        <v>91150</v>
+        <v>100364</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511689</v>
+        <v>511790</v>
       </c>
       <c r="R17" t="n">
-        <v>6733823</v>
+        <v>6733915</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2275,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216529</v>
+        <v>121216564</v>
       </c>
       <c r="B18" t="n">
-        <v>91150</v>
+        <v>100364</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511778</v>
+        <v>511683</v>
       </c>
       <c r="R18" t="n">
-        <v>6733902</v>
+        <v>6733794</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2377,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216525</v>
+        <v>121216559</v>
       </c>
       <c r="B19" t="n">
-        <v>91150</v>
+        <v>100364</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511722</v>
+        <v>511701</v>
       </c>
       <c r="R19" t="n">
-        <v>6733810</v>
+        <v>6733806</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216578</v>
+        <v>121216534</v>
       </c>
       <c r="B20" t="n">
-        <v>100361</v>
+        <v>90999</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511790</v>
+        <v>511691</v>
       </c>
       <c r="R20" t="n">
-        <v>6733915</v>
+        <v>6733814</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216503</v>
+        <v>121216545</v>
       </c>
       <c r="B21" t="n">
-        <v>90710</v>
+        <v>90727</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511689</v>
+        <v>511749</v>
       </c>
       <c r="R21" t="n">
-        <v>6733823</v>
+        <v>6733943</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,6 +2694,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216547</v>
+        <v>121216493</v>
       </c>
       <c r="B22" t="n">
-        <v>90728</v>
+        <v>95645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511698</v>
+        <v>511719</v>
       </c>
       <c r="R22" t="n">
-        <v>6733774</v>
+        <v>6733820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216573</v>
+        <v>121216570</v>
       </c>
       <c r="B23" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511712</v>
+        <v>511737</v>
       </c>
       <c r="R23" t="n">
-        <v>6733910</v>
+        <v>6733875</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216572</v>
+        <v>121216579</v>
       </c>
       <c r="B24" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511717</v>
+        <v>511786</v>
       </c>
       <c r="R24" t="n">
-        <v>6733894</v>
+        <v>6733947</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216535</v>
+        <v>121216566</v>
       </c>
       <c r="B25" t="n">
-        <v>90996</v>
+        <v>100364</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511681</v>
+        <v>511692</v>
       </c>
       <c r="R25" t="n">
-        <v>6733814</v>
+        <v>6733799</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216550</v>
+        <v>121216520</v>
       </c>
       <c r="B26" t="n">
-        <v>90728</v>
+        <v>91153</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,7 +3173,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511697</v>
+        <v>511694</v>
       </c>
       <c r="R26" t="n">
         <v>6733776</v>
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216583</v>
+        <v>121216536</v>
       </c>
       <c r="B27" t="n">
-        <v>5169</v>
+        <v>90999</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,43 +3247,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511712</v>
+        <v>511766</v>
       </c>
       <c r="R27" t="n">
-        <v>6733841</v>
+        <v>6733889</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,7 +3300,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3332,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216577</v>
+        <v>121216550</v>
       </c>
       <c r="B28" t="n">
-        <v>100361</v>
+        <v>90731</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511753</v>
+        <v>511697</v>
       </c>
       <c r="R28" t="n">
-        <v>6733916</v>
+        <v>6733776</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,7 +3402,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3434,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216575</v>
+        <v>121216507</v>
       </c>
       <c r="B29" t="n">
-        <v>100361</v>
+        <v>90713</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511726</v>
+        <v>511767</v>
       </c>
       <c r="R29" t="n">
-        <v>6733920</v>
+        <v>6733888</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,7 +3504,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3536,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216580</v>
+        <v>121216494</v>
       </c>
       <c r="B30" t="n">
-        <v>100361</v>
+        <v>90678</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511773</v>
+        <v>511695</v>
       </c>
       <c r="R30" t="n">
-        <v>6733953</v>
+        <v>6733800</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216501</v>
+        <v>121216504</v>
       </c>
       <c r="B31" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3678,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511692</v>
+        <v>511683</v>
       </c>
       <c r="R31" t="n">
-        <v>6733805</v>
+        <v>6733814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216545</v>
+        <v>121216522</v>
       </c>
       <c r="B32" t="n">
-        <v>90724</v>
+        <v>91153</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511749</v>
+        <v>511691</v>
       </c>
       <c r="R32" t="n">
-        <v>6733943</v>
+        <v>6733814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3816,11 +3821,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216502</v>
+        <v>121216525</v>
       </c>
       <c r="B33" t="n">
-        <v>90710</v>
+        <v>91153</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3859,25 +3859,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511691</v>
+        <v>511722</v>
       </c>
       <c r="R33" t="n">
-        <v>6733814</v>
+        <v>6733810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216531</v>
+        <v>121216547</v>
       </c>
       <c r="B34" t="n">
-        <v>90996</v>
+        <v>90731</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511682</v>
+        <v>511698</v>
       </c>
       <c r="R34" t="n">
-        <v>6733773</v>
+        <v>6733774</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216495</v>
+        <v>121216572</v>
       </c>
       <c r="B35" t="n">
-        <v>90675</v>
+        <v>100364</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4067,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511704</v>
+        <v>511717</v>
       </c>
       <c r="R35" t="n">
-        <v>6733869</v>
+        <v>6733894</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216570</v>
+        <v>121216577</v>
       </c>
       <c r="B36" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511737</v>
+        <v>511753</v>
       </c>
       <c r="R36" t="n">
-        <v>6733875</v>
+        <v>6733916</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216581</v>
+        <v>121216527</v>
       </c>
       <c r="B37" t="n">
-        <v>100361</v>
+        <v>91153</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511749</v>
+        <v>511722</v>
       </c>
       <c r="R37" t="n">
-        <v>6733964</v>
+        <v>6733823</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216571</v>
+        <v>121216503</v>
       </c>
       <c r="B38" t="n">
-        <v>100361</v>
+        <v>90713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511735</v>
+        <v>511689</v>
       </c>
       <c r="R38" t="n">
-        <v>6733890</v>
+        <v>6733823</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216519</v>
+        <v>121216529</v>
       </c>
       <c r="B39" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511684</v>
+        <v>511778</v>
       </c>
       <c r="R39" t="n">
-        <v>6733782</v>
+        <v>6733902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4561,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216552</v>
+        <v>121216581</v>
       </c>
       <c r="B40" t="n">
-        <v>90728</v>
+        <v>100364</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4573,25 +4573,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511717</v>
+        <v>511749</v>
       </c>
       <c r="R40" t="n">
-        <v>6733907</v>
+        <v>6733964</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216520</v>
+        <v>121216569</v>
       </c>
       <c r="B41" t="n">
-        <v>91150</v>
+        <v>100364</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511694</v>
+        <v>511726</v>
       </c>
       <c r="R41" t="n">
-        <v>6733776</v>
+        <v>6733897</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4765,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216544</v>
+        <v>121216509</v>
       </c>
       <c r="B42" t="n">
-        <v>90724</v>
+        <v>90713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511752</v>
+        <v>511760</v>
       </c>
       <c r="R42" t="n">
-        <v>6733939</v>
+        <v>6733909</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4841,11 +4841,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4872,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216524</v>
+        <v>121216505</v>
       </c>
       <c r="B43" t="n">
-        <v>91150</v>
+        <v>90713</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4879,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511679</v>
+        <v>511703</v>
       </c>
       <c r="R43" t="n">
-        <v>6733815</v>
+        <v>6733823</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216553</v>
+        <v>121216513</v>
       </c>
       <c r="B44" t="n">
-        <v>90728</v>
+        <v>57370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4990,34 +4985,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511738</v>
+        <v>511726</v>
       </c>
       <c r="R44" t="n">
-        <v>6733948</v>
+        <v>6733944</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216565</v>
+        <v>121216575</v>
       </c>
       <c r="B45" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511692</v>
+        <v>511726</v>
       </c>
       <c r="R45" t="n">
-        <v>6733786</v>
+        <v>6733920</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216507</v>
+        <v>121216583</v>
       </c>
       <c r="B46" t="n">
-        <v>90710</v>
+        <v>5172</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,38 +5190,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511767</v>
+        <v>511712</v>
       </c>
       <c r="R46" t="n">
-        <v>6733888</v>
+        <v>6733841</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5280,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216534</v>
+        <v>121216573</v>
       </c>
       <c r="B47" t="n">
-        <v>90996</v>
+        <v>100364</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5297,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511691</v>
+        <v>511712</v>
       </c>
       <c r="R47" t="n">
-        <v>6733814</v>
+        <v>6733910</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5382,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216494</v>
+        <v>121216519</v>
       </c>
       <c r="B48" t="n">
-        <v>90675</v>
+        <v>91153</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5394,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511695</v>
+        <v>511684</v>
       </c>
       <c r="R48" t="n">
-        <v>6733800</v>
+        <v>6733782</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216576</v>
+        <v>121216571</v>
       </c>
       <c r="B49" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5527,7 +5532,7 @@
         <v>511735</v>
       </c>
       <c r="R49" t="n">
-        <v>6733932</v>
+        <v>6733890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5586,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216559</v>
+        <v>121216565</v>
       </c>
       <c r="B50" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511701</v>
+        <v>511692</v>
       </c>
       <c r="R50" t="n">
-        <v>6733806</v>
+        <v>6733786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5651,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5691,7 +5696,7 @@
         <v>121216533</v>
       </c>
       <c r="B51" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5790,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216508</v>
+        <v>121216535</v>
       </c>
       <c r="B52" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5806,21 +5811,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511778</v>
+        <v>511681</v>
       </c>
       <c r="R52" t="n">
-        <v>6733888</v>
+        <v>6733814</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5855,7 +5860,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5892,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216566</v>
+        <v>121216495</v>
       </c>
       <c r="B53" t="n">
-        <v>100361</v>
+        <v>90678</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5908,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511692</v>
+        <v>511704</v>
       </c>
       <c r="R53" t="n">
-        <v>6733799</v>
+        <v>6733869</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5994,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216509</v>
+        <v>121216553</v>
       </c>
       <c r="B54" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6010,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511760</v>
+        <v>511738</v>
       </c>
       <c r="R54" t="n">
-        <v>6733909</v>
+        <v>6733948</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6096,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216513</v>
+        <v>121216521</v>
       </c>
       <c r="B55" t="n">
-        <v>57367</v>
+        <v>91153</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6108,43 +6113,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511726</v>
+        <v>511691</v>
       </c>
       <c r="R55" t="n">
-        <v>6733944</v>
+        <v>6733805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
         <v>121216538</v>
       </c>
       <c r="B56" t="n">
-        <v>91783</v>
+        <v>91786</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6308,6 +6308,218 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121513842</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90713</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>511691</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6733807</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121513982</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91153</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>511694</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6733768</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216580</v>
+        <v>121216550</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511773</v>
+        <v>511697</v>
       </c>
       <c r="R2" t="n">
-        <v>6733953</v>
+        <v>6733776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216568</v>
+        <v>121216527</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>91153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511706</v>
+        <v>511722</v>
       </c>
       <c r="R3" t="n">
-        <v>6733883</v>
+        <v>6733823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216551</v>
+        <v>121216525</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>91153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511719</v>
+        <v>511722</v>
       </c>
       <c r="R4" t="n">
-        <v>6733835</v>
+        <v>6733810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216552</v>
+        <v>121216505</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511717</v>
+        <v>511703</v>
       </c>
       <c r="R5" t="n">
-        <v>6733907</v>
+        <v>6733823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216508</v>
+        <v>121216501</v>
       </c>
       <c r="B6" t="n">
         <v>90713</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511778</v>
+        <v>511692</v>
       </c>
       <c r="R6" t="n">
-        <v>6733888</v>
+        <v>6733805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216501</v>
+        <v>121216534</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>90999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511692</v>
+        <v>511691</v>
       </c>
       <c r="R7" t="n">
-        <v>6733805</v>
+        <v>6733814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216524</v>
+        <v>121216579</v>
       </c>
       <c r="B8" t="n">
-        <v>91153</v>
+        <v>100364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511679</v>
+        <v>511786</v>
       </c>
       <c r="R8" t="n">
-        <v>6733815</v>
+        <v>6733947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216531</v>
+        <v>121216570</v>
       </c>
       <c r="B9" t="n">
-        <v>90999</v>
+        <v>100364</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511682</v>
+        <v>511737</v>
       </c>
       <c r="R9" t="n">
-        <v>6733773</v>
+        <v>6733875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216567</v>
+        <v>121216529</v>
       </c>
       <c r="B10" t="n">
-        <v>100364</v>
+        <v>91153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511717</v>
+        <v>511778</v>
       </c>
       <c r="R10" t="n">
-        <v>6733840</v>
+        <v>6733902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216544</v>
+        <v>121216521</v>
       </c>
       <c r="B11" t="n">
-        <v>90727</v>
+        <v>91153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511752</v>
+        <v>511691</v>
       </c>
       <c r="R11" t="n">
-        <v>6733939</v>
+        <v>6733805</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1669,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216526</v>
+        <v>121216535</v>
       </c>
       <c r="B13" t="n">
-        <v>91153</v>
+        <v>90999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511715</v>
+        <v>511681</v>
       </c>
       <c r="R13" t="n">
-        <v>6733819</v>
+        <v>6733814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216576</v>
+        <v>121216531</v>
       </c>
       <c r="B14" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511735</v>
+        <v>511682</v>
       </c>
       <c r="R14" t="n">
-        <v>6733932</v>
+        <v>6733773</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216512</v>
+        <v>121216581</v>
       </c>
       <c r="B15" t="n">
-        <v>90660</v>
+        <v>100364</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>112</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511791</v>
+        <v>511749</v>
       </c>
       <c r="R15" t="n">
-        <v>6733958</v>
+        <v>6733964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216502</v>
+        <v>121216578</v>
       </c>
       <c r="B16" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511691</v>
+        <v>511790</v>
       </c>
       <c r="R16" t="n">
-        <v>6733814</v>
+        <v>6733915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2168,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216578</v>
+        <v>121216568</v>
       </c>
       <c r="B17" t="n">
         <v>100364</v>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511790</v>
+        <v>511706</v>
       </c>
       <c r="R17" t="n">
-        <v>6733915</v>
+        <v>6733883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,7 +2270,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216564</v>
+        <v>121216551</v>
       </c>
       <c r="B18" t="n">
-        <v>100364</v>
+        <v>90731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511683</v>
+        <v>511719</v>
       </c>
       <c r="R18" t="n">
-        <v>6733794</v>
+        <v>6733835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216559</v>
+        <v>121216504</v>
       </c>
       <c r="B19" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511701</v>
+        <v>511683</v>
       </c>
       <c r="R19" t="n">
-        <v>6733806</v>
+        <v>6733814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216534</v>
+        <v>121216495</v>
       </c>
       <c r="B20" t="n">
-        <v>90999</v>
+        <v>90678</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511691</v>
+        <v>511704</v>
       </c>
       <c r="R20" t="n">
-        <v>6733814</v>
+        <v>6733869</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216545</v>
+        <v>121216520</v>
       </c>
       <c r="B21" t="n">
-        <v>90727</v>
+        <v>91153</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511749</v>
+        <v>511694</v>
       </c>
       <c r="R21" t="n">
-        <v>6733943</v>
+        <v>6733776</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,7 +2678,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2694,11 +2689,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216493</v>
+        <v>121216566</v>
       </c>
       <c r="B22" t="n">
-        <v>95645</v>
+        <v>100364</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511719</v>
+        <v>511692</v>
       </c>
       <c r="R22" t="n">
-        <v>6733820</v>
+        <v>6733799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2780,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216570</v>
+        <v>121216502</v>
       </c>
       <c r="B23" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511737</v>
+        <v>511691</v>
       </c>
       <c r="R23" t="n">
-        <v>6733875</v>
+        <v>6733814</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216579</v>
+        <v>121216519</v>
       </c>
       <c r="B24" t="n">
-        <v>100364</v>
+        <v>91153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511786</v>
+        <v>511684</v>
       </c>
       <c r="R24" t="n">
-        <v>6733947</v>
+        <v>6733782</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216566</v>
+        <v>121216508</v>
       </c>
       <c r="B25" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3033,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511692</v>
+        <v>511778</v>
       </c>
       <c r="R25" t="n">
-        <v>6733799</v>
+        <v>6733888</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3096,7 +3086,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216520</v>
+        <v>121216507</v>
       </c>
       <c r="B26" t="n">
-        <v>91153</v>
+        <v>90713</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511694</v>
+        <v>511767</v>
       </c>
       <c r="R26" t="n">
-        <v>6733776</v>
+        <v>6733888</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216536</v>
+        <v>121216575</v>
       </c>
       <c r="B27" t="n">
-        <v>90999</v>
+        <v>100364</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3237,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511766</v>
+        <v>511726</v>
       </c>
       <c r="R27" t="n">
-        <v>6733889</v>
+        <v>6733920</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3300,7 +3290,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3337,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216550</v>
+        <v>121216552</v>
       </c>
       <c r="B28" t="n">
         <v>90731</v>
@@ -3377,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511697</v>
+        <v>511717</v>
       </c>
       <c r="R28" t="n">
-        <v>6733776</v>
+        <v>6733907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3402,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3439,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216507</v>
+        <v>121216493</v>
       </c>
       <c r="B29" t="n">
-        <v>90713</v>
+        <v>95645</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511767</v>
+        <v>511719</v>
       </c>
       <c r="R29" t="n">
-        <v>6733888</v>
+        <v>6733820</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216494</v>
+        <v>121216544</v>
       </c>
       <c r="B30" t="n">
-        <v>90678</v>
+        <v>90727</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3543,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511695</v>
+        <v>511752</v>
       </c>
       <c r="R30" t="n">
-        <v>6733800</v>
+        <v>6733939</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3617,6 +3607,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3643,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216504</v>
+        <v>121216573</v>
       </c>
       <c r="B31" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3650,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511683</v>
+        <v>511712</v>
       </c>
       <c r="R31" t="n">
-        <v>6733814</v>
+        <v>6733910</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,7 +3740,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216522</v>
+        <v>121216526</v>
       </c>
       <c r="B32" t="n">
         <v>91153</v>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511691</v>
+        <v>511715</v>
       </c>
       <c r="R32" t="n">
-        <v>6733814</v>
+        <v>6733819</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,7 +3805,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3847,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216525</v>
+        <v>121216509</v>
       </c>
       <c r="B33" t="n">
-        <v>91153</v>
+        <v>90713</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3859,25 +3854,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511722</v>
+        <v>511760</v>
       </c>
       <c r="R33" t="n">
-        <v>6733810</v>
+        <v>6733909</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,7 +3907,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3949,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216547</v>
+        <v>121216545</v>
       </c>
       <c r="B34" t="n">
-        <v>90731</v>
+        <v>90727</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511698</v>
+        <v>511749</v>
       </c>
       <c r="R34" t="n">
-        <v>6733774</v>
+        <v>6733943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4014,7 +4009,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4025,6 +4020,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4051,7 +4051,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216572</v>
+        <v>121216580</v>
       </c>
       <c r="B35" t="n">
         <v>100364</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511717</v>
+        <v>511773</v>
       </c>
       <c r="R35" t="n">
-        <v>6733894</v>
+        <v>6733953</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216577</v>
+        <v>121216569</v>
       </c>
       <c r="B36" t="n">
         <v>100364</v>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511753</v>
+        <v>511726</v>
       </c>
       <c r="R36" t="n">
-        <v>6733916</v>
+        <v>6733897</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216527</v>
+        <v>121216577</v>
       </c>
       <c r="B37" t="n">
-        <v>91153</v>
+        <v>100364</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511722</v>
+        <v>511753</v>
       </c>
       <c r="R37" t="n">
-        <v>6733823</v>
+        <v>6733916</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216503</v>
+        <v>121216512</v>
       </c>
       <c r="B38" t="n">
-        <v>90713</v>
+        <v>90660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4373,21 +4373,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511689</v>
+        <v>511791</v>
       </c>
       <c r="R38" t="n">
-        <v>6733823</v>
+        <v>6733958</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216529</v>
+        <v>121216513</v>
       </c>
       <c r="B39" t="n">
-        <v>91153</v>
+        <v>57370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,38 +4471,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511778</v>
+        <v>511726</v>
       </c>
       <c r="R39" t="n">
-        <v>6733902</v>
+        <v>6733944</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4524,7 +4529,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4561,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216581</v>
+        <v>121216553</v>
       </c>
       <c r="B40" t="n">
-        <v>100364</v>
+        <v>90731</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4573,25 +4578,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511749</v>
+        <v>511738</v>
       </c>
       <c r="R40" t="n">
-        <v>6733964</v>
+        <v>6733948</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216569</v>
+        <v>121216522</v>
       </c>
       <c r="B41" t="n">
-        <v>100364</v>
+        <v>91153</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4675,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511726</v>
+        <v>511691</v>
       </c>
       <c r="R41" t="n">
-        <v>6733897</v>
+        <v>6733814</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216509</v>
+        <v>121216576</v>
       </c>
       <c r="B42" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4777,25 +4782,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511760</v>
+        <v>511735</v>
       </c>
       <c r="R42" t="n">
-        <v>6733909</v>
+        <v>6733932</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4867,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216505</v>
+        <v>121216559</v>
       </c>
       <c r="B43" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4879,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4907,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511703</v>
+        <v>511701</v>
       </c>
       <c r="R43" t="n">
-        <v>6733823</v>
+        <v>6733806</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216513</v>
+        <v>121216564</v>
       </c>
       <c r="B44" t="n">
-        <v>57370</v>
+        <v>100364</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4981,43 +4986,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511726</v>
+        <v>511683</v>
       </c>
       <c r="R44" t="n">
-        <v>6733944</v>
+        <v>6733794</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,7 +5076,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216575</v>
+        <v>121216565</v>
       </c>
       <c r="B45" t="n">
         <v>100364</v>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511726</v>
+        <v>511692</v>
       </c>
       <c r="R45" t="n">
-        <v>6733920</v>
+        <v>6733786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5285,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216573</v>
+        <v>121216536</v>
       </c>
       <c r="B47" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,25 +5297,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511712</v>
+        <v>511766</v>
       </c>
       <c r="R47" t="n">
-        <v>6733910</v>
+        <v>6733889</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216519</v>
+        <v>121216547</v>
       </c>
       <c r="B48" t="n">
-        <v>91153</v>
+        <v>90731</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511684</v>
+        <v>511698</v>
       </c>
       <c r="R48" t="n">
-        <v>6733782</v>
+        <v>6733774</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5489,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216571</v>
+        <v>121216494</v>
       </c>
       <c r="B49" t="n">
-        <v>100364</v>
+        <v>90678</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511735</v>
+        <v>511695</v>
       </c>
       <c r="R49" t="n">
-        <v>6733890</v>
+        <v>6733800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216565</v>
+        <v>121216533</v>
       </c>
       <c r="B50" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5603,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511692</v>
+        <v>511683</v>
       </c>
       <c r="R50" t="n">
-        <v>6733786</v>
+        <v>6733782</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216533</v>
+        <v>121216503</v>
       </c>
       <c r="B51" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511683</v>
+        <v>511689</v>
       </c>
       <c r="R51" t="n">
-        <v>6733782</v>
+        <v>6733823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216535</v>
+        <v>121216572</v>
       </c>
       <c r="B52" t="n">
-        <v>90999</v>
+        <v>100364</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511681</v>
+        <v>511717</v>
       </c>
       <c r="R52" t="n">
-        <v>6733814</v>
+        <v>6733894</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216495</v>
+        <v>121216571</v>
       </c>
       <c r="B53" t="n">
-        <v>90678</v>
+        <v>100364</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511704</v>
+        <v>511735</v>
       </c>
       <c r="R53" t="n">
-        <v>6733869</v>
+        <v>6733890</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216553</v>
+        <v>121216524</v>
       </c>
       <c r="B54" t="n">
-        <v>90731</v>
+        <v>91153</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,25 +6011,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511738</v>
+        <v>511679</v>
       </c>
       <c r="R54" t="n">
-        <v>6733948</v>
+        <v>6733815</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216521</v>
+        <v>121216567</v>
       </c>
       <c r="B55" t="n">
-        <v>91153</v>
+        <v>100364</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6113,25 +6113,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511691</v>
+        <v>511717</v>
       </c>
       <c r="R55" t="n">
-        <v>6733805</v>
+        <v>6733840</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6311,10 +6311,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121513842</v>
+        <v>121513982</v>
       </c>
       <c r="B57" t="n">
-        <v>90713</v>
+        <v>91153</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6323,25 +6323,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>511691</v>
+        <v>511694</v>
       </c>
       <c r="R57" t="n">
-        <v>6733807</v>
+        <v>6733768</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -6417,10 +6417,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121513982</v>
+        <v>121528011</v>
       </c>
       <c r="B58" t="n">
-        <v>91153</v>
+        <v>57354</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6429,44 +6429,53 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Stor Moberg, Kilen-Stor, Moberg, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>511694</v>
+        <v>511671</v>
       </c>
       <c r="R58" t="n">
-        <v>6733768</v>
+        <v>6733661</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6504,19 +6513,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216550</v>
+        <v>121216527</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>91153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511697</v>
+        <v>511722</v>
       </c>
       <c r="R2" t="n">
-        <v>6733776</v>
+        <v>6733823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216527</v>
+        <v>121216525</v>
       </c>
       <c r="B3" t="n">
         <v>91153</v>
@@ -820,7 +820,7 @@
         <v>511722</v>
       </c>
       <c r="R3" t="n">
-        <v>6733823</v>
+        <v>6733810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216525</v>
+        <v>121216505</v>
       </c>
       <c r="B4" t="n">
-        <v>91153</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511722</v>
+        <v>511703</v>
       </c>
       <c r="R4" t="n">
-        <v>6733810</v>
+        <v>6733823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216505</v>
+        <v>121216501</v>
       </c>
       <c r="B5" t="n">
         <v>90713</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511703</v>
+        <v>511692</v>
       </c>
       <c r="R5" t="n">
-        <v>6733823</v>
+        <v>6733805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216501</v>
+        <v>121216534</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>90999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511692</v>
+        <v>511691</v>
       </c>
       <c r="R6" t="n">
-        <v>6733805</v>
+        <v>6733814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216534</v>
+        <v>121216550</v>
       </c>
       <c r="B7" t="n">
-        <v>90999</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511691</v>
+        <v>511697</v>
       </c>
       <c r="R7" t="n">
-        <v>6733814</v>
+        <v>6733776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216523</v>
+        <v>121216581</v>
       </c>
       <c r="B12" t="n">
-        <v>91153</v>
+        <v>100364</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511689</v>
+        <v>511749</v>
       </c>
       <c r="R12" t="n">
-        <v>6733823</v>
+        <v>6733964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216535</v>
+        <v>121216578</v>
       </c>
       <c r="B13" t="n">
-        <v>90999</v>
+        <v>100364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511681</v>
+        <v>511790</v>
       </c>
       <c r="R13" t="n">
-        <v>6733814</v>
+        <v>6733915</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216531</v>
+        <v>121216568</v>
       </c>
       <c r="B14" t="n">
-        <v>90999</v>
+        <v>100364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511682</v>
+        <v>511706</v>
       </c>
       <c r="R14" t="n">
-        <v>6733773</v>
+        <v>6733883</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216581</v>
+        <v>121216523</v>
       </c>
       <c r="B15" t="n">
-        <v>100364</v>
+        <v>91153</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511749</v>
+        <v>511689</v>
       </c>
       <c r="R15" t="n">
-        <v>6733964</v>
+        <v>6733823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216578</v>
+        <v>121216535</v>
       </c>
       <c r="B16" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511790</v>
+        <v>511681</v>
       </c>
       <c r="R16" t="n">
-        <v>6733915</v>
+        <v>6733814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216568</v>
+        <v>121216531</v>
       </c>
       <c r="B17" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511706</v>
+        <v>511682</v>
       </c>
       <c r="R17" t="n">
-        <v>6733883</v>
+        <v>6733773</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216493</v>
+        <v>121216573</v>
       </c>
       <c r="B29" t="n">
-        <v>95645</v>
+        <v>100364</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3441,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511719</v>
+        <v>511712</v>
       </c>
       <c r="R29" t="n">
-        <v>6733820</v>
+        <v>6733910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216544</v>
+        <v>121216493</v>
       </c>
       <c r="B30" t="n">
-        <v>90727</v>
+        <v>95645</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511752</v>
+        <v>511719</v>
       </c>
       <c r="R30" t="n">
-        <v>6733939</v>
+        <v>6733820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3607,11 +3607,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3638,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216573</v>
+        <v>121216544</v>
       </c>
       <c r="B31" t="n">
-        <v>100364</v>
+        <v>90727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3650,25 +3645,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511712</v>
+        <v>511752</v>
       </c>
       <c r="R31" t="n">
-        <v>6733910</v>
+        <v>6733939</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,6 +3709,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216547</v>
+        <v>121216572</v>
       </c>
       <c r="B48" t="n">
-        <v>90731</v>
+        <v>100364</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511698</v>
+        <v>511717</v>
       </c>
       <c r="R48" t="n">
-        <v>6733774</v>
+        <v>6733894</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5489,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216494</v>
+        <v>121216571</v>
       </c>
       <c r="B49" t="n">
-        <v>90678</v>
+        <v>100364</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511695</v>
+        <v>511735</v>
       </c>
       <c r="R49" t="n">
-        <v>6733800</v>
+        <v>6733890</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216533</v>
+        <v>121216547</v>
       </c>
       <c r="B50" t="n">
-        <v>90999</v>
+        <v>90731</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511683</v>
+        <v>511698</v>
       </c>
       <c r="R50" t="n">
-        <v>6733782</v>
+        <v>6733774</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216503</v>
+        <v>121216494</v>
       </c>
       <c r="B51" t="n">
-        <v>90713</v>
+        <v>90678</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511689</v>
+        <v>511695</v>
       </c>
       <c r="R51" t="n">
-        <v>6733823</v>
+        <v>6733800</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216572</v>
+        <v>121216533</v>
       </c>
       <c r="B52" t="n">
-        <v>100364</v>
+        <v>90999</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511717</v>
+        <v>511683</v>
       </c>
       <c r="R52" t="n">
-        <v>6733894</v>
+        <v>6733782</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216571</v>
+        <v>121216503</v>
       </c>
       <c r="B53" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511735</v>
+        <v>511689</v>
       </c>
       <c r="R53" t="n">
-        <v>6733890</v>
+        <v>6733823</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6529,6 +6529,108 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121216543</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56558</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>511703</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6733869</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216527</v>
+        <v>121216550</v>
       </c>
       <c r="B2" t="n">
-        <v>91153</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511722</v>
+        <v>511697</v>
       </c>
       <c r="R2" t="n">
-        <v>6733823</v>
+        <v>6733776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216525</v>
+        <v>121216527</v>
       </c>
       <c r="B3" t="n">
         <v>91153</v>
@@ -820,7 +820,7 @@
         <v>511722</v>
       </c>
       <c r="R3" t="n">
-        <v>6733810</v>
+        <v>6733823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216505</v>
+        <v>121216525</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>91153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511703</v>
+        <v>511722</v>
       </c>
       <c r="R4" t="n">
-        <v>6733823</v>
+        <v>6733810</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216501</v>
+        <v>121216505</v>
       </c>
       <c r="B5" t="n">
         <v>90713</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511692</v>
+        <v>511703</v>
       </c>
       <c r="R5" t="n">
-        <v>6733805</v>
+        <v>6733823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216534</v>
+        <v>121216501</v>
       </c>
       <c r="B6" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511691</v>
+        <v>511692</v>
       </c>
       <c r="R6" t="n">
-        <v>6733814</v>
+        <v>6733805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216550</v>
+        <v>121216534</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>90999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511697</v>
+        <v>511691</v>
       </c>
       <c r="R7" t="n">
-        <v>6733776</v>
+        <v>6733814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216551</v>
+        <v>121216504</v>
       </c>
       <c r="B18" t="n">
-        <v>90731</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511719</v>
+        <v>511683</v>
       </c>
       <c r="R18" t="n">
-        <v>6733835</v>
+        <v>6733814</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216504</v>
+        <v>121216551</v>
       </c>
       <c r="B19" t="n">
-        <v>90713</v>
+        <v>90731</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511683</v>
+        <v>511719</v>
       </c>
       <c r="R19" t="n">
-        <v>6733814</v>
+        <v>6733835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216495</v>
+        <v>121216520</v>
       </c>
       <c r="B20" t="n">
-        <v>90678</v>
+        <v>91153</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511704</v>
+        <v>511694</v>
       </c>
       <c r="R20" t="n">
-        <v>6733869</v>
+        <v>6733776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216520</v>
+        <v>121216495</v>
       </c>
       <c r="B21" t="n">
-        <v>91153</v>
+        <v>90678</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511694</v>
+        <v>511704</v>
       </c>
       <c r="R21" t="n">
-        <v>6733776</v>
+        <v>6733869</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216583</v>
+        <v>121216536</v>
       </c>
       <c r="B46" t="n">
-        <v>5172</v>
+        <v>90999</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,43 +5190,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511712</v>
+        <v>511766</v>
       </c>
       <c r="R46" t="n">
-        <v>6733841</v>
+        <v>6733889</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5285,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216536</v>
+        <v>121216583</v>
       </c>
       <c r="B47" t="n">
-        <v>90999</v>
+        <v>5172</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,38 +5292,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511766</v>
+        <v>511712</v>
       </c>
       <c r="R47" t="n">
-        <v>6733889</v>
+        <v>6733841</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216572</v>
+        <v>121216547</v>
       </c>
       <c r="B48" t="n">
-        <v>100364</v>
+        <v>90731</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511717</v>
+        <v>511698</v>
       </c>
       <c r="R48" t="n">
-        <v>6733894</v>
+        <v>6733774</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5489,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216571</v>
+        <v>121216494</v>
       </c>
       <c r="B49" t="n">
-        <v>100364</v>
+        <v>90678</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511735</v>
+        <v>511695</v>
       </c>
       <c r="R49" t="n">
-        <v>6733890</v>
+        <v>6733800</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216547</v>
+        <v>121216533</v>
       </c>
       <c r="B50" t="n">
-        <v>90731</v>
+        <v>90999</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511698</v>
+        <v>511683</v>
       </c>
       <c r="R50" t="n">
-        <v>6733774</v>
+        <v>6733782</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216494</v>
+        <v>121216503</v>
       </c>
       <c r="B51" t="n">
-        <v>90678</v>
+        <v>90713</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511695</v>
+        <v>511689</v>
       </c>
       <c r="R51" t="n">
-        <v>6733800</v>
+        <v>6733823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216533</v>
+        <v>121216572</v>
       </c>
       <c r="B52" t="n">
-        <v>90999</v>
+        <v>100364</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511683</v>
+        <v>511717</v>
       </c>
       <c r="R52" t="n">
-        <v>6733782</v>
+        <v>6733894</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216503</v>
+        <v>121216571</v>
       </c>
       <c r="B53" t="n">
-        <v>90713</v>
+        <v>100364</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511689</v>
+        <v>511735</v>
       </c>
       <c r="R53" t="n">
-        <v>6733823</v>
+        <v>6733890</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216550</v>
+        <v>121216535</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>91005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511697</v>
+        <v>511681</v>
       </c>
       <c r="R2" t="n">
-        <v>6733776</v>
+        <v>6733814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216527</v>
+        <v>121216579</v>
       </c>
       <c r="B3" t="n">
-        <v>91153</v>
+        <v>100370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511722</v>
+        <v>511786</v>
       </c>
       <c r="R3" t="n">
-        <v>6733823</v>
+        <v>6733947</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216525</v>
+        <v>121216527</v>
       </c>
       <c r="B4" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>511722</v>
       </c>
       <c r="R4" t="n">
-        <v>6733810</v>
+        <v>6733823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216505</v>
+        <v>121216575</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511703</v>
+        <v>511726</v>
       </c>
       <c r="R5" t="n">
-        <v>6733823</v>
+        <v>6733920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216501</v>
+        <v>121216571</v>
       </c>
       <c r="B6" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511692</v>
+        <v>511735</v>
       </c>
       <c r="R6" t="n">
-        <v>6733805</v>
+        <v>6733890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216534</v>
+        <v>121216526</v>
       </c>
       <c r="B7" t="n">
-        <v>90999</v>
+        <v>91159</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511691</v>
+        <v>511715</v>
       </c>
       <c r="R7" t="n">
-        <v>6733814</v>
+        <v>6733819</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216579</v>
+        <v>121216581</v>
       </c>
       <c r="B8" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511786</v>
+        <v>511749</v>
       </c>
       <c r="R8" t="n">
-        <v>6733947</v>
+        <v>6733964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216570</v>
+        <v>121216565</v>
       </c>
       <c r="B9" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511737</v>
+        <v>511692</v>
       </c>
       <c r="R9" t="n">
-        <v>6733875</v>
+        <v>6733786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216529</v>
+        <v>121216534</v>
       </c>
       <c r="B10" t="n">
-        <v>91153</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511778</v>
+        <v>511691</v>
       </c>
       <c r="R10" t="n">
-        <v>6733902</v>
+        <v>6733814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216521</v>
+        <v>121216522</v>
       </c>
       <c r="B11" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>511691</v>
       </c>
       <c r="R11" t="n">
-        <v>6733805</v>
+        <v>6733814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216581</v>
+        <v>121216502</v>
       </c>
       <c r="B12" t="n">
-        <v>100364</v>
+        <v>90719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511749</v>
+        <v>511691</v>
       </c>
       <c r="R12" t="n">
-        <v>6733964</v>
+        <v>6733814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216578</v>
+        <v>121216513</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>57371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,38 +1809,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511790</v>
+        <v>511726</v>
       </c>
       <c r="R13" t="n">
-        <v>6733915</v>
+        <v>6733944</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1867,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216568</v>
+        <v>121216493</v>
       </c>
       <c r="B14" t="n">
-        <v>100364</v>
+        <v>95651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511706</v>
+        <v>511719</v>
       </c>
       <c r="R14" t="n">
-        <v>6733883</v>
+        <v>6733820</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216523</v>
+        <v>121216570</v>
       </c>
       <c r="B15" t="n">
-        <v>91153</v>
+        <v>100370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511689</v>
+        <v>511737</v>
       </c>
       <c r="R15" t="n">
-        <v>6733823</v>
+        <v>6733875</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216535</v>
+        <v>121216569</v>
       </c>
       <c r="B16" t="n">
-        <v>90999</v>
+        <v>100370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511681</v>
+        <v>511726</v>
       </c>
       <c r="R16" t="n">
-        <v>6733814</v>
+        <v>6733897</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216531</v>
+        <v>121216524</v>
       </c>
       <c r="B17" t="n">
-        <v>90999</v>
+        <v>91159</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511682</v>
+        <v>511679</v>
       </c>
       <c r="R17" t="n">
-        <v>6733773</v>
+        <v>6733815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2275,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2307,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216504</v>
+        <v>121216572</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511683</v>
+        <v>511717</v>
       </c>
       <c r="R18" t="n">
-        <v>6733814</v>
+        <v>6733894</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216551</v>
+        <v>121216507</v>
       </c>
       <c r="B19" t="n">
-        <v>90731</v>
+        <v>90719</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511719</v>
+        <v>511767</v>
       </c>
       <c r="R19" t="n">
-        <v>6733835</v>
+        <v>6733888</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216520</v>
+        <v>121216512</v>
       </c>
       <c r="B20" t="n">
-        <v>91153</v>
+        <v>90666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511694</v>
+        <v>511791</v>
       </c>
       <c r="R20" t="n">
-        <v>6733776</v>
+        <v>6733958</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2581,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2613,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216495</v>
+        <v>121216503</v>
       </c>
       <c r="B21" t="n">
-        <v>90678</v>
+        <v>90719</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511704</v>
+        <v>511689</v>
       </c>
       <c r="R21" t="n">
-        <v>6733869</v>
+        <v>6733823</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216566</v>
+        <v>121216583</v>
       </c>
       <c r="B22" t="n">
-        <v>100364</v>
+        <v>5172</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,34 +2736,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511692</v>
+        <v>511712</v>
       </c>
       <c r="R22" t="n">
-        <v>6733799</v>
+        <v>6733841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216502</v>
+        <v>121216577</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511691</v>
+        <v>511753</v>
       </c>
       <c r="R23" t="n">
-        <v>6733814</v>
+        <v>6733916</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216519</v>
+        <v>121216573</v>
       </c>
       <c r="B24" t="n">
-        <v>91153</v>
+        <v>100370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2931,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511684</v>
+        <v>511712</v>
       </c>
       <c r="R24" t="n">
-        <v>6733782</v>
+        <v>6733910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216508</v>
+        <v>121216580</v>
       </c>
       <c r="B25" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511778</v>
+        <v>511773</v>
       </c>
       <c r="R25" t="n">
-        <v>6733888</v>
+        <v>6733953</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,7 +3096,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216507</v>
+        <v>121216576</v>
       </c>
       <c r="B26" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3135,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511767</v>
+        <v>511735</v>
       </c>
       <c r="R26" t="n">
-        <v>6733888</v>
+        <v>6733932</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,7 +3198,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216575</v>
+        <v>121216551</v>
       </c>
       <c r="B27" t="n">
-        <v>100364</v>
+        <v>90737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3247,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511726</v>
+        <v>511719</v>
       </c>
       <c r="R27" t="n">
-        <v>6733920</v>
+        <v>6733835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216552</v>
+        <v>121216559</v>
       </c>
       <c r="B28" t="n">
-        <v>90731</v>
+        <v>100370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511717</v>
+        <v>511701</v>
       </c>
       <c r="R28" t="n">
-        <v>6733907</v>
+        <v>6733806</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216573</v>
+        <v>121216578</v>
       </c>
       <c r="B29" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511712</v>
+        <v>511790</v>
       </c>
       <c r="R29" t="n">
-        <v>6733910</v>
+        <v>6733915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,7 +3504,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3531,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216493</v>
+        <v>121216547</v>
       </c>
       <c r="B30" t="n">
-        <v>95645</v>
+        <v>90737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511719</v>
+        <v>511698</v>
       </c>
       <c r="R30" t="n">
-        <v>6733820</v>
+        <v>6733774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216544</v>
+        <v>121216508</v>
       </c>
       <c r="B31" t="n">
-        <v>90727</v>
+        <v>90719</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511752</v>
+        <v>511778</v>
       </c>
       <c r="R31" t="n">
-        <v>6733939</v>
+        <v>6733888</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3698,7 +3708,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3709,11 +3719,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3740,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216526</v>
+        <v>121216519</v>
       </c>
       <c r="B32" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511715</v>
+        <v>511684</v>
       </c>
       <c r="R32" t="n">
-        <v>6733819</v>
+        <v>6733782</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,7 +3810,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3842,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216509</v>
+        <v>121216533</v>
       </c>
       <c r="B33" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511760</v>
+        <v>511683</v>
       </c>
       <c r="R33" t="n">
-        <v>6733909</v>
+        <v>6733782</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216545</v>
+        <v>121216504</v>
       </c>
       <c r="B34" t="n">
-        <v>90727</v>
+        <v>90719</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511749</v>
+        <v>511683</v>
       </c>
       <c r="R34" t="n">
-        <v>6733943</v>
+        <v>6733814</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,11 +4025,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4051,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216580</v>
+        <v>121216523</v>
       </c>
       <c r="B35" t="n">
-        <v>100364</v>
+        <v>91159</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,25 +4063,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511773</v>
+        <v>511689</v>
       </c>
       <c r="R35" t="n">
-        <v>6733953</v>
+        <v>6733823</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216569</v>
+        <v>121216525</v>
       </c>
       <c r="B36" t="n">
-        <v>100364</v>
+        <v>91159</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511726</v>
+        <v>511722</v>
       </c>
       <c r="R36" t="n">
-        <v>6733897</v>
+        <v>6733810</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216577</v>
+        <v>121216520</v>
       </c>
       <c r="B37" t="n">
-        <v>100364</v>
+        <v>91159</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511753</v>
+        <v>511694</v>
       </c>
       <c r="R37" t="n">
-        <v>6733916</v>
+        <v>6733776</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216512</v>
+        <v>121216529</v>
       </c>
       <c r="B38" t="n">
-        <v>90660</v>
+        <v>91159</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>112</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511791</v>
+        <v>511778</v>
       </c>
       <c r="R38" t="n">
-        <v>6733958</v>
+        <v>6733902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4459,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216513</v>
+        <v>121216495</v>
       </c>
       <c r="B39" t="n">
-        <v>57370</v>
+        <v>90684</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,43 +4471,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511726</v>
+        <v>511704</v>
       </c>
       <c r="R39" t="n">
-        <v>6733944</v>
+        <v>6733869</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4569,7 +4564,7 @@
         <v>121216553</v>
       </c>
       <c r="B40" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4668,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216522</v>
+        <v>121216505</v>
       </c>
       <c r="B41" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511691</v>
+        <v>511703</v>
       </c>
       <c r="R41" t="n">
-        <v>6733814</v>
+        <v>6733823</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216576</v>
+        <v>121216545</v>
       </c>
       <c r="B42" t="n">
-        <v>100364</v>
+        <v>90733</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4782,25 +4777,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511735</v>
+        <v>511749</v>
       </c>
       <c r="R42" t="n">
-        <v>6733932</v>
+        <v>6733943</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4846,6 +4841,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216559</v>
+        <v>121216536</v>
       </c>
       <c r="B43" t="n">
-        <v>100364</v>
+        <v>91005</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511701</v>
+        <v>511766</v>
       </c>
       <c r="R43" t="n">
-        <v>6733806</v>
+        <v>6733889</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216564</v>
+        <v>121216568</v>
       </c>
       <c r="B44" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511683</v>
+        <v>511706</v>
       </c>
       <c r="R44" t="n">
-        <v>6733794</v>
+        <v>6733883</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5076,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216565</v>
+        <v>121216531</v>
       </c>
       <c r="B45" t="n">
-        <v>100364</v>
+        <v>91005</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5088,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511692</v>
+        <v>511682</v>
       </c>
       <c r="R45" t="n">
-        <v>6733786</v>
+        <v>6733773</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5178,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216536</v>
+        <v>121216494</v>
       </c>
       <c r="B46" t="n">
-        <v>90999</v>
+        <v>90684</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,25 +5190,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511766</v>
+        <v>511695</v>
       </c>
       <c r="R46" t="n">
-        <v>6733889</v>
+        <v>6733800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216583</v>
+        <v>121216544</v>
       </c>
       <c r="B47" t="n">
-        <v>5172</v>
+        <v>90733</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,43 +5292,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511712</v>
+        <v>511752</v>
       </c>
       <c r="R47" t="n">
-        <v>6733841</v>
+        <v>6733939</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5361,6 +5356,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216547</v>
+        <v>121216521</v>
       </c>
       <c r="B48" t="n">
-        <v>90731</v>
+        <v>91159</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511698</v>
+        <v>511691</v>
       </c>
       <c r="R48" t="n">
-        <v>6733774</v>
+        <v>6733805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5489,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216494</v>
+        <v>121216567</v>
       </c>
       <c r="B49" t="n">
-        <v>90678</v>
+        <v>100370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511695</v>
+        <v>511717</v>
       </c>
       <c r="R49" t="n">
-        <v>6733800</v>
+        <v>6733840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216533</v>
+        <v>121216550</v>
       </c>
       <c r="B50" t="n">
-        <v>90999</v>
+        <v>90737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511683</v>
+        <v>511697</v>
       </c>
       <c r="R50" t="n">
-        <v>6733782</v>
+        <v>6733776</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216503</v>
+        <v>121216552</v>
       </c>
       <c r="B51" t="n">
-        <v>90713</v>
+        <v>90737</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511689</v>
+        <v>511717</v>
       </c>
       <c r="R51" t="n">
-        <v>6733823</v>
+        <v>6733907</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216572</v>
+        <v>121216564</v>
       </c>
       <c r="B52" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511717</v>
+        <v>511683</v>
       </c>
       <c r="R52" t="n">
-        <v>6733894</v>
+        <v>6733794</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216571</v>
+        <v>121216509</v>
       </c>
       <c r="B53" t="n">
-        <v>100364</v>
+        <v>90719</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511735</v>
+        <v>511760</v>
       </c>
       <c r="R53" t="n">
-        <v>6733890</v>
+        <v>6733909</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216524</v>
+        <v>121216501</v>
       </c>
       <c r="B54" t="n">
-        <v>91153</v>
+        <v>90719</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,25 +6011,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511679</v>
+        <v>511692</v>
       </c>
       <c r="R54" t="n">
-        <v>6733815</v>
+        <v>6733805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216567</v>
+        <v>121216566</v>
       </c>
       <c r="B55" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511717</v>
+        <v>511692</v>
       </c>
       <c r="R55" t="n">
-        <v>6733840</v>
+        <v>6733799</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
         <v>121216538</v>
       </c>
       <c r="B56" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>121513982</v>
       </c>
       <c r="B57" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>121528011</v>
       </c>
       <c r="B58" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>121216543</v>
       </c>
       <c r="B59" t="n">
-        <v>56558</v>
+        <v>56559</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216526</v>
+        <v>121216534</v>
       </c>
       <c r="B7" t="n">
-        <v>91159</v>
+        <v>91005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511715</v>
+        <v>511691</v>
       </c>
       <c r="R7" t="n">
-        <v>6733819</v>
+        <v>6733814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216581</v>
+        <v>121216526</v>
       </c>
       <c r="B8" t="n">
-        <v>100370</v>
+        <v>91159</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511749</v>
+        <v>511715</v>
       </c>
       <c r="R8" t="n">
-        <v>6733964</v>
+        <v>6733819</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216565</v>
+        <v>121216581</v>
       </c>
       <c r="B9" t="n">
         <v>100370</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511692</v>
+        <v>511749</v>
       </c>
       <c r="R9" t="n">
-        <v>6733786</v>
+        <v>6733964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216534</v>
+        <v>121216565</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>100370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511691</v>
+        <v>511692</v>
       </c>
       <c r="R10" t="n">
-        <v>6733814</v>
+        <v>6733786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216536</v>
+        <v>121216568</v>
       </c>
       <c r="B43" t="n">
-        <v>91005</v>
+        <v>100370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511766</v>
+        <v>511706</v>
       </c>
       <c r="R43" t="n">
-        <v>6733889</v>
+        <v>6733883</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216568</v>
+        <v>121216536</v>
       </c>
       <c r="B44" t="n">
-        <v>100370</v>
+        <v>91005</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511706</v>
+        <v>511766</v>
       </c>
       <c r="R44" t="n">
-        <v>6733883</v>
+        <v>6733889</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216535</v>
+        <v>121216523</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
+        <v>91160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511681</v>
+        <v>511689</v>
       </c>
       <c r="R2" t="n">
-        <v>6733814</v>
+        <v>6733823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216579</v>
+        <v>121216547</v>
       </c>
       <c r="B3" t="n">
-        <v>100370</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511786</v>
+        <v>511698</v>
       </c>
       <c r="R3" t="n">
-        <v>6733947</v>
+        <v>6733774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216527</v>
+        <v>121216571</v>
       </c>
       <c r="B4" t="n">
-        <v>91159</v>
+        <v>100371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511722</v>
+        <v>511735</v>
       </c>
       <c r="R4" t="n">
-        <v>6733823</v>
+        <v>6733890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216575</v>
+        <v>121216526</v>
       </c>
       <c r="B5" t="n">
-        <v>100370</v>
+        <v>91160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511726</v>
+        <v>511715</v>
       </c>
       <c r="R5" t="n">
-        <v>6733920</v>
+        <v>6733819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216571</v>
+        <v>121216531</v>
       </c>
       <c r="B6" t="n">
-        <v>100370</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511735</v>
+        <v>511682</v>
       </c>
       <c r="R6" t="n">
-        <v>6733890</v>
+        <v>6733773</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216534</v>
+        <v>121216508</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511691</v>
+        <v>511778</v>
       </c>
       <c r="R7" t="n">
-        <v>6733814</v>
+        <v>6733888</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216526</v>
+        <v>121216524</v>
       </c>
       <c r="B8" t="n">
-        <v>91159</v>
+        <v>91160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511715</v>
+        <v>511679</v>
       </c>
       <c r="R8" t="n">
-        <v>6733819</v>
+        <v>6733815</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216581</v>
+        <v>121216569</v>
       </c>
       <c r="B9" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511749</v>
+        <v>511726</v>
       </c>
       <c r="R9" t="n">
-        <v>6733964</v>
+        <v>6733897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216565</v>
+        <v>121216550</v>
       </c>
       <c r="B10" t="n">
-        <v>100370</v>
+        <v>90738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511692</v>
+        <v>511697</v>
       </c>
       <c r="R10" t="n">
-        <v>6733786</v>
+        <v>6733776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216522</v>
+        <v>121216552</v>
       </c>
       <c r="B11" t="n">
-        <v>91159</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511691</v>
+        <v>511717</v>
       </c>
       <c r="R11" t="n">
-        <v>6733814</v>
+        <v>6733907</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216502</v>
+        <v>121216493</v>
       </c>
       <c r="B12" t="n">
-        <v>90719</v>
+        <v>95652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511691</v>
+        <v>511719</v>
       </c>
       <c r="R12" t="n">
-        <v>6733814</v>
+        <v>6733820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216513</v>
+        <v>121216495</v>
       </c>
       <c r="B13" t="n">
-        <v>57371</v>
+        <v>90685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,43 +1809,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511726</v>
+        <v>511704</v>
       </c>
       <c r="R13" t="n">
-        <v>6733944</v>
+        <v>6733869</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216493</v>
+        <v>121216513</v>
       </c>
       <c r="B14" t="n">
-        <v>95651</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,34 +1915,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511719</v>
+        <v>511726</v>
       </c>
       <c r="R14" t="n">
-        <v>6733820</v>
+        <v>6733944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216570</v>
+        <v>121216507</v>
       </c>
       <c r="B15" t="n">
-        <v>100370</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511737</v>
+        <v>511767</v>
       </c>
       <c r="R15" t="n">
-        <v>6733875</v>
+        <v>6733888</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216569</v>
+        <v>121216529</v>
       </c>
       <c r="B16" t="n">
-        <v>100370</v>
+        <v>91160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511726</v>
+        <v>511778</v>
       </c>
       <c r="R16" t="n">
-        <v>6733897</v>
+        <v>6733902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216524</v>
+        <v>121216583</v>
       </c>
       <c r="B17" t="n">
-        <v>91159</v>
+        <v>5172</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,38 +2222,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511679</v>
+        <v>511712</v>
       </c>
       <c r="R17" t="n">
-        <v>6733815</v>
+        <v>6733841</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216572</v>
+        <v>121216567</v>
       </c>
       <c r="B18" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,7 +2360,7 @@
         <v>511717</v>
       </c>
       <c r="R18" t="n">
-        <v>6733894</v>
+        <v>6733840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216507</v>
+        <v>121216581</v>
       </c>
       <c r="B19" t="n">
-        <v>90719</v>
+        <v>100371</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511767</v>
+        <v>511749</v>
       </c>
       <c r="R19" t="n">
-        <v>6733888</v>
+        <v>6733964</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2484,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216512</v>
+        <v>121216578</v>
       </c>
       <c r="B20" t="n">
-        <v>90666</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511791</v>
+        <v>511790</v>
       </c>
       <c r="R20" t="n">
-        <v>6733958</v>
+        <v>6733915</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,7 +2586,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216503</v>
+        <v>121216512</v>
       </c>
       <c r="B21" t="n">
-        <v>90719</v>
+        <v>90667</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511689</v>
+        <v>511791</v>
       </c>
       <c r="R21" t="n">
-        <v>6733823</v>
+        <v>6733958</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216583</v>
+        <v>121216525</v>
       </c>
       <c r="B22" t="n">
-        <v>5172</v>
+        <v>91160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,43 +2737,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511712</v>
+        <v>511722</v>
       </c>
       <c r="R22" t="n">
-        <v>6733841</v>
+        <v>6733810</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2830,7 +2830,7 @@
         <v>121216577</v>
       </c>
       <c r="B23" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216573</v>
+        <v>121216522</v>
       </c>
       <c r="B24" t="n">
-        <v>100370</v>
+        <v>91160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511712</v>
+        <v>511691</v>
       </c>
       <c r="R24" t="n">
-        <v>6733910</v>
+        <v>6733814</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216580</v>
+        <v>121216534</v>
       </c>
       <c r="B25" t="n">
-        <v>100370</v>
+        <v>91006</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511773</v>
+        <v>511691</v>
       </c>
       <c r="R25" t="n">
-        <v>6733953</v>
+        <v>6733814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216576</v>
+        <v>121216536</v>
       </c>
       <c r="B26" t="n">
-        <v>100370</v>
+        <v>91006</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511735</v>
+        <v>511766</v>
       </c>
       <c r="R26" t="n">
-        <v>6733932</v>
+        <v>6733889</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216551</v>
+        <v>121216535</v>
       </c>
       <c r="B27" t="n">
-        <v>90737</v>
+        <v>91006</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511719</v>
+        <v>511681</v>
       </c>
       <c r="R27" t="n">
-        <v>6733835</v>
+        <v>6733814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216559</v>
+        <v>121216494</v>
       </c>
       <c r="B28" t="n">
-        <v>100370</v>
+        <v>90685</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511701</v>
+        <v>511695</v>
       </c>
       <c r="R28" t="n">
-        <v>6733806</v>
+        <v>6733800</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216578</v>
+        <v>121216551</v>
       </c>
       <c r="B29" t="n">
-        <v>100370</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511790</v>
+        <v>511719</v>
       </c>
       <c r="R29" t="n">
-        <v>6733915</v>
+        <v>6733835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216547</v>
+        <v>121216566</v>
       </c>
       <c r="B30" t="n">
-        <v>90737</v>
+        <v>100371</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511698</v>
+        <v>511692</v>
       </c>
       <c r="R30" t="n">
-        <v>6733774</v>
+        <v>6733799</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216508</v>
+        <v>121216559</v>
       </c>
       <c r="B31" t="n">
-        <v>90719</v>
+        <v>100371</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511778</v>
+        <v>511701</v>
       </c>
       <c r="R31" t="n">
-        <v>6733888</v>
+        <v>6733806</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216519</v>
+        <v>121216568</v>
       </c>
       <c r="B32" t="n">
-        <v>91159</v>
+        <v>100371</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511684</v>
+        <v>511706</v>
       </c>
       <c r="R32" t="n">
-        <v>6733782</v>
+        <v>6733883</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216533</v>
+        <v>121216544</v>
       </c>
       <c r="B33" t="n">
-        <v>91005</v>
+        <v>90734</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511683</v>
+        <v>511752</v>
       </c>
       <c r="R33" t="n">
-        <v>6733782</v>
+        <v>6733939</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3923,6 +3923,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3949,10 +3954,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216504</v>
+        <v>121216503</v>
       </c>
       <c r="B34" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3989,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511683</v>
+        <v>511689</v>
       </c>
       <c r="R34" t="n">
-        <v>6733814</v>
+        <v>6733823</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,10 +4056,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216523</v>
+        <v>121216579</v>
       </c>
       <c r="B35" t="n">
-        <v>91159</v>
+        <v>100371</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,25 +4068,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511689</v>
+        <v>511786</v>
       </c>
       <c r="R35" t="n">
-        <v>6733823</v>
+        <v>6733947</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,10 +4158,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216525</v>
+        <v>121216572</v>
       </c>
       <c r="B36" t="n">
-        <v>91159</v>
+        <v>100371</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4165,25 +4170,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511722</v>
+        <v>511717</v>
       </c>
       <c r="R36" t="n">
-        <v>6733810</v>
+        <v>6733894</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4218,7 +4223,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4255,10 +4260,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121216520</v>
+        <v>121216575</v>
       </c>
       <c r="B37" t="n">
-        <v>91159</v>
+        <v>100371</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,25 +4272,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>511694</v>
+        <v>511726</v>
       </c>
       <c r="R37" t="n">
-        <v>6733776</v>
+        <v>6733920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4357,10 +4362,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121216529</v>
+        <v>121216533</v>
       </c>
       <c r="B38" t="n">
-        <v>91159</v>
+        <v>91006</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,25 +4374,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511778</v>
+        <v>511683</v>
       </c>
       <c r="R38" t="n">
-        <v>6733902</v>
+        <v>6733782</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4427,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4459,10 +4464,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216495</v>
+        <v>121216570</v>
       </c>
       <c r="B39" t="n">
-        <v>90684</v>
+        <v>100371</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4475,21 +4480,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511704</v>
+        <v>511737</v>
       </c>
       <c r="R39" t="n">
-        <v>6733869</v>
+        <v>6733875</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216553</v>
+        <v>121216504</v>
       </c>
       <c r="B40" t="n">
-        <v>90737</v>
+        <v>90720</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4577,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511738</v>
+        <v>511683</v>
       </c>
       <c r="R40" t="n">
-        <v>6733948</v>
+        <v>6733814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4663,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216505</v>
+        <v>121216545</v>
       </c>
       <c r="B41" t="n">
-        <v>90719</v>
+        <v>90734</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4679,21 +4684,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4703,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511703</v>
+        <v>511749</v>
       </c>
       <c r="R41" t="n">
-        <v>6733823</v>
+        <v>6733943</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,6 +4744,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4765,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216545</v>
+        <v>121216501</v>
       </c>
       <c r="B42" t="n">
-        <v>90733</v>
+        <v>90720</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4791,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,10 +4815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511749</v>
+        <v>511692</v>
       </c>
       <c r="R42" t="n">
-        <v>6733943</v>
+        <v>6733805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4841,11 +4851,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4872,10 +4877,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216568</v>
+        <v>121216580</v>
       </c>
       <c r="B43" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511706</v>
+        <v>511773</v>
       </c>
       <c r="R43" t="n">
-        <v>6733883</v>
+        <v>6733953</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4979,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216536</v>
+        <v>121216502</v>
       </c>
       <c r="B44" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4990,21 +4995,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511766</v>
+        <v>511691</v>
       </c>
       <c r="R44" t="n">
-        <v>6733889</v>
+        <v>6733814</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,7 +5044,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5076,10 +5081,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216531</v>
+        <v>121216519</v>
       </c>
       <c r="B45" t="n">
-        <v>91005</v>
+        <v>91160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5093,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511682</v>
+        <v>511684</v>
       </c>
       <c r="R45" t="n">
-        <v>6733773</v>
+        <v>6733782</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5141,7 +5146,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5178,10 +5183,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216494</v>
+        <v>121216520</v>
       </c>
       <c r="B46" t="n">
-        <v>90684</v>
+        <v>91160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,25 +5195,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511695</v>
+        <v>511694</v>
       </c>
       <c r="R46" t="n">
-        <v>6733800</v>
+        <v>6733776</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5280,10 +5285,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216544</v>
+        <v>121216565</v>
       </c>
       <c r="B47" t="n">
-        <v>90733</v>
+        <v>100371</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5292,25 +5297,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511752</v>
+        <v>511692</v>
       </c>
       <c r="R47" t="n">
-        <v>6733939</v>
+        <v>6733786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5345,7 +5350,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5356,11 +5361,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216521</v>
+        <v>121216505</v>
       </c>
       <c r="B48" t="n">
-        <v>91159</v>
+        <v>90720</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511691</v>
+        <v>511703</v>
       </c>
       <c r="R48" t="n">
-        <v>6733805</v>
+        <v>6733823</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,10 +5489,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216567</v>
+        <v>121216573</v>
       </c>
       <c r="B49" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511717</v>
+        <v>511712</v>
       </c>
       <c r="R49" t="n">
-        <v>6733840</v>
+        <v>6733910</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216550</v>
+        <v>121216564</v>
       </c>
       <c r="B50" t="n">
-        <v>90737</v>
+        <v>100371</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5603,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511697</v>
+        <v>511683</v>
       </c>
       <c r="R50" t="n">
-        <v>6733776</v>
+        <v>6733794</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216552</v>
+        <v>121216527</v>
       </c>
       <c r="B51" t="n">
-        <v>90737</v>
+        <v>91160</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511717</v>
+        <v>511722</v>
       </c>
       <c r="R51" t="n">
-        <v>6733907</v>
+        <v>6733823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216564</v>
+        <v>121216521</v>
       </c>
       <c r="B52" t="n">
-        <v>100370</v>
+        <v>91160</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5807,25 +5807,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511683</v>
+        <v>511691</v>
       </c>
       <c r="R52" t="n">
-        <v>6733794</v>
+        <v>6733805</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216509</v>
+        <v>121216553</v>
       </c>
       <c r="B53" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511760</v>
+        <v>511738</v>
       </c>
       <c r="R53" t="n">
-        <v>6733909</v>
+        <v>6733948</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216501</v>
+        <v>121216509</v>
       </c>
       <c r="B54" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511692</v>
+        <v>511760</v>
       </c>
       <c r="R54" t="n">
-        <v>6733805</v>
+        <v>6733909</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216566</v>
+        <v>121216576</v>
       </c>
       <c r="B55" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>511692</v>
+        <v>511735</v>
       </c>
       <c r="R55" t="n">
-        <v>6733799</v>
+        <v>6733932</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
         <v>121216538</v>
       </c>
       <c r="B56" t="n">
-        <v>91792</v>
+        <v>91793</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>121513982</v>
       </c>
       <c r="B57" t="n">
-        <v>91159</v>
+        <v>91160</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>121528011</v>
       </c>
       <c r="B58" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>121216543</v>
       </c>
       <c r="B59" t="n">
-        <v>56559</v>
+        <v>56560</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121216523</v>
+        <v>121216494</v>
       </c>
       <c r="B2" t="n">
-        <v>91160</v>
+        <v>90685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511689</v>
+        <v>511695</v>
       </c>
       <c r="R2" t="n">
-        <v>6733823</v>
+        <v>6733800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121216547</v>
+        <v>121216504</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511698</v>
+        <v>511683</v>
       </c>
       <c r="R3" t="n">
-        <v>6733774</v>
+        <v>6733814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121216571</v>
+        <v>121216536</v>
       </c>
       <c r="B4" t="n">
-        <v>100371</v>
+        <v>91006</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511735</v>
+        <v>511766</v>
       </c>
       <c r="R4" t="n">
-        <v>6733890</v>
+        <v>6733889</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121216526</v>
+        <v>121216559</v>
       </c>
       <c r="B5" t="n">
-        <v>91160</v>
+        <v>100371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511715</v>
+        <v>511701</v>
       </c>
       <c r="R5" t="n">
-        <v>6733819</v>
+        <v>6733806</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121216531</v>
+        <v>121216569</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>100371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511682</v>
+        <v>511726</v>
       </c>
       <c r="R6" t="n">
-        <v>6733773</v>
+        <v>6733897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121216508</v>
+        <v>121216552</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511778</v>
+        <v>511717</v>
       </c>
       <c r="R7" t="n">
-        <v>6733888</v>
+        <v>6733907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121216524</v>
+        <v>121216545</v>
       </c>
       <c r="B8" t="n">
-        <v>91160</v>
+        <v>90734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511679</v>
+        <v>511749</v>
       </c>
       <c r="R8" t="n">
-        <v>6733815</v>
+        <v>6733943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121216569</v>
+        <v>121216583</v>
       </c>
       <c r="B9" t="n">
-        <v>100371</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1410,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511726</v>
+        <v>511712</v>
       </c>
       <c r="R9" t="n">
-        <v>6733897</v>
+        <v>6733841</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121216550</v>
+        <v>121216572</v>
       </c>
       <c r="B10" t="n">
-        <v>90738</v>
+        <v>100371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511697</v>
+        <v>511717</v>
       </c>
       <c r="R10" t="n">
-        <v>6733776</v>
+        <v>6733894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1566,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121216552</v>
+        <v>121216531</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>91006</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511717</v>
+        <v>511682</v>
       </c>
       <c r="R11" t="n">
-        <v>6733907</v>
+        <v>6733773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1668,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121216493</v>
+        <v>121216519</v>
       </c>
       <c r="B12" t="n">
-        <v>95652</v>
+        <v>91160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511719</v>
+        <v>511684</v>
       </c>
       <c r="R12" t="n">
-        <v>6733820</v>
+        <v>6733782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1770,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1797,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121216495</v>
+        <v>121216529</v>
       </c>
       <c r="B13" t="n">
-        <v>90685</v>
+        <v>91160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511704</v>
+        <v>511778</v>
       </c>
       <c r="R13" t="n">
-        <v>6733869</v>
+        <v>6733902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1872,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121216513</v>
+        <v>121216566</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,43 +1921,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511726</v>
+        <v>511692</v>
       </c>
       <c r="R14" t="n">
-        <v>6733944</v>
+        <v>6733799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121216507</v>
+        <v>121216581</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>100371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511767</v>
+        <v>511749</v>
       </c>
       <c r="R15" t="n">
-        <v>6733888</v>
+        <v>6733964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2076,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121216529</v>
+        <v>121216502</v>
       </c>
       <c r="B16" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2125,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511778</v>
+        <v>511691</v>
       </c>
       <c r="R16" t="n">
-        <v>6733902</v>
+        <v>6733814</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,7 +2178,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121216583</v>
+        <v>121216565</v>
       </c>
       <c r="B17" t="n">
-        <v>5172</v>
+        <v>100371</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,39 +2231,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511712</v>
+        <v>511692</v>
       </c>
       <c r="R17" t="n">
-        <v>6733841</v>
+        <v>6733786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121216567</v>
+        <v>121216527</v>
       </c>
       <c r="B18" t="n">
-        <v>100371</v>
+        <v>91160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2329,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511717</v>
+        <v>511722</v>
       </c>
       <c r="R18" t="n">
-        <v>6733840</v>
+        <v>6733823</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121216581</v>
+        <v>121216505</v>
       </c>
       <c r="B19" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511749</v>
+        <v>511703</v>
       </c>
       <c r="R19" t="n">
-        <v>6733964</v>
+        <v>6733823</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121216578</v>
+        <v>121216564</v>
       </c>
       <c r="B20" t="n">
         <v>100371</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511790</v>
+        <v>511683</v>
       </c>
       <c r="R20" t="n">
-        <v>6733915</v>
+        <v>6733794</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121216512</v>
+        <v>121216568</v>
       </c>
       <c r="B21" t="n">
-        <v>90667</v>
+        <v>100371</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511791</v>
+        <v>511706</v>
       </c>
       <c r="R21" t="n">
-        <v>6733958</v>
+        <v>6733883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121216525</v>
+        <v>121216567</v>
       </c>
       <c r="B22" t="n">
-        <v>91160</v>
+        <v>100371</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511722</v>
+        <v>511717</v>
       </c>
       <c r="R22" t="n">
-        <v>6733810</v>
+        <v>6733840</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121216577</v>
+        <v>121216550</v>
       </c>
       <c r="B23" t="n">
-        <v>100371</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511753</v>
+        <v>511697</v>
       </c>
       <c r="R23" t="n">
-        <v>6733916</v>
+        <v>6733776</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121216522</v>
+        <v>121216521</v>
       </c>
       <c r="B24" t="n">
         <v>91160</v>
@@ -2972,7 +2972,7 @@
         <v>511691</v>
       </c>
       <c r="R24" t="n">
-        <v>6733814</v>
+        <v>6733805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121216534</v>
+        <v>121216512</v>
       </c>
       <c r="B25" t="n">
-        <v>91006</v>
+        <v>90667</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511691</v>
+        <v>511791</v>
       </c>
       <c r="R25" t="n">
-        <v>6733814</v>
+        <v>6733958</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121216536</v>
+        <v>121216534</v>
       </c>
       <c r="B26" t="n">
         <v>91006</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511766</v>
+        <v>511691</v>
       </c>
       <c r="R26" t="n">
-        <v>6733889</v>
+        <v>6733814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121216535</v>
+        <v>121216503</v>
       </c>
       <c r="B27" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511681</v>
+        <v>511689</v>
       </c>
       <c r="R27" t="n">
-        <v>6733814</v>
+        <v>6733823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121216494</v>
+        <v>121216553</v>
       </c>
       <c r="B28" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511695</v>
+        <v>511738</v>
       </c>
       <c r="R28" t="n">
-        <v>6733800</v>
+        <v>6733948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121216551</v>
+        <v>121216524</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>91160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511719</v>
+        <v>511679</v>
       </c>
       <c r="R29" t="n">
-        <v>6733835</v>
+        <v>6733815</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121216566</v>
+        <v>121216579</v>
       </c>
       <c r="B30" t="n">
         <v>100371</v>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511692</v>
+        <v>511786</v>
       </c>
       <c r="R30" t="n">
-        <v>6733799</v>
+        <v>6733947</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121216559</v>
+        <v>121216501</v>
       </c>
       <c r="B31" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511701</v>
+        <v>511692</v>
       </c>
       <c r="R31" t="n">
-        <v>6733806</v>
+        <v>6733805</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121216568</v>
+        <v>121216522</v>
       </c>
       <c r="B32" t="n">
-        <v>100371</v>
+        <v>91160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>511706</v>
+        <v>511691</v>
       </c>
       <c r="R32" t="n">
-        <v>6733883</v>
+        <v>6733814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121216544</v>
+        <v>121216507</v>
       </c>
       <c r="B33" t="n">
-        <v>90734</v>
+        <v>90720</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511752</v>
+        <v>511767</v>
       </c>
       <c r="R33" t="n">
-        <v>6733939</v>
+        <v>6733888</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3923,11 +3923,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3954,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121216503</v>
+        <v>121216493</v>
       </c>
       <c r="B34" t="n">
-        <v>90720</v>
+        <v>95652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3970,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3994,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511689</v>
+        <v>511719</v>
       </c>
       <c r="R34" t="n">
-        <v>6733823</v>
+        <v>6733820</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4019,7 +4014,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4056,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121216579</v>
+        <v>121216509</v>
       </c>
       <c r="B35" t="n">
-        <v>100371</v>
+        <v>90720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4068,25 +4063,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4096,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>511786</v>
+        <v>511760</v>
       </c>
       <c r="R35" t="n">
-        <v>6733947</v>
+        <v>6733909</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4158,7 +4153,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121216572</v>
+        <v>121216580</v>
       </c>
       <c r="B36" t="n">
         <v>100371</v>
@@ -4198,10 +4193,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>511717</v>
+        <v>511773</v>
       </c>
       <c r="R36" t="n">
-        <v>6733894</v>
+        <v>6733953</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121216570</v>
+        <v>121216523</v>
       </c>
       <c r="B39" t="n">
-        <v>100371</v>
+        <v>91160</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4476,25 +4471,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511737</v>
+        <v>511689</v>
       </c>
       <c r="R39" t="n">
-        <v>6733875</v>
+        <v>6733823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4561,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121216504</v>
+        <v>121216508</v>
       </c>
       <c r="B40" t="n">
         <v>90720</v>
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511683</v>
+        <v>511778</v>
       </c>
       <c r="R40" t="n">
-        <v>6733814</v>
+        <v>6733888</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,7 +4626,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4668,10 +4663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121216545</v>
+        <v>121216578</v>
       </c>
       <c r="B41" t="n">
-        <v>90734</v>
+        <v>100371</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511749</v>
+        <v>511790</v>
       </c>
       <c r="R41" t="n">
-        <v>6733943</v>
+        <v>6733915</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4733,7 +4728,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4744,11 +4739,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4775,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121216501</v>
+        <v>121216535</v>
       </c>
       <c r="B42" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>511692</v>
+        <v>511681</v>
       </c>
       <c r="R42" t="n">
-        <v>6733805</v>
+        <v>6733814</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121216580</v>
+        <v>121216544</v>
       </c>
       <c r="B43" t="n">
-        <v>100371</v>
+        <v>90734</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4889,25 +4879,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511773</v>
+        <v>511752</v>
       </c>
       <c r="R43" t="n">
-        <v>6733953</v>
+        <v>6733939</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4953,6 +4943,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På timmerstock</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4979,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121216502</v>
+        <v>121216520</v>
       </c>
       <c r="B44" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4991,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511691</v>
+        <v>511694</v>
       </c>
       <c r="R44" t="n">
-        <v>6733814</v>
+        <v>6733776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5044,7 +5039,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121216519</v>
+        <v>121216570</v>
       </c>
       <c r="B45" t="n">
-        <v>91160</v>
+        <v>100371</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5093,25 +5088,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>511684</v>
+        <v>511737</v>
       </c>
       <c r="R45" t="n">
-        <v>6733782</v>
+        <v>6733875</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121216520</v>
+        <v>121216513</v>
       </c>
       <c r="B46" t="n">
-        <v>91160</v>
+        <v>57372</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5195,38 +5190,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>511694</v>
+        <v>511726</v>
       </c>
       <c r="R46" t="n">
-        <v>6733776</v>
+        <v>6733944</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5285,7 +5285,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121216565</v>
+        <v>121216573</v>
       </c>
       <c r="B47" t="n">
         <v>100371</v>
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>511692</v>
+        <v>511712</v>
       </c>
       <c r="R47" t="n">
-        <v>6733786</v>
+        <v>6733910</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121216505</v>
+        <v>121216576</v>
       </c>
       <c r="B48" t="n">
-        <v>90720</v>
+        <v>100371</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>511703</v>
+        <v>511735</v>
       </c>
       <c r="R48" t="n">
-        <v>6733823</v>
+        <v>6733932</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121216573</v>
+        <v>121216577</v>
       </c>
       <c r="B49" t="n">
         <v>100371</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>511712</v>
+        <v>511753</v>
       </c>
       <c r="R49" t="n">
-        <v>6733910</v>
+        <v>6733916</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5591,10 +5591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121216564</v>
+        <v>121216495</v>
       </c>
       <c r="B50" t="n">
-        <v>100371</v>
+        <v>90685</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,21 +5607,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>511683</v>
+        <v>511704</v>
       </c>
       <c r="R50" t="n">
-        <v>6733794</v>
+        <v>6733869</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5693,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121216527</v>
+        <v>121216551</v>
       </c>
       <c r="B51" t="n">
-        <v>91160</v>
+        <v>90738</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5705,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>511722</v>
+        <v>511719</v>
       </c>
       <c r="R51" t="n">
-        <v>6733823</v>
+        <v>6733835</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Bjursås</t>
+          <t>Leksand</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5795,7 +5795,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121216521</v>
+        <v>121216525</v>
       </c>
       <c r="B52" t="n">
         <v>91160</v>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>511691</v>
+        <v>511722</v>
       </c>
       <c r="R52" t="n">
-        <v>6733805</v>
+        <v>6733810</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -5897,10 +5897,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121216553</v>
+        <v>121216526</v>
       </c>
       <c r="B53" t="n">
-        <v>90738</v>
+        <v>91160</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5909,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>511738</v>
+        <v>511715</v>
       </c>
       <c r="R53" t="n">
-        <v>6733948</v>
+        <v>6733819</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121216509</v>
+        <v>121216547</v>
       </c>
       <c r="B54" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>511760</v>
+        <v>511698</v>
       </c>
       <c r="R54" t="n">
-        <v>6733909</v>
+        <v>6733774</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Leksand</t>
+          <t>Bjursås</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -6101,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121216576</v>
+        <v>121216571</v>
       </c>
       <c r="B55" t="n">
         <v>100371</v>
@@ -6144,7 +6144,7 @@
         <v>511735</v>
       </c>
       <c r="R55" t="n">
-        <v>6733932</v>
+        <v>6733890</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -6314,7 +6314,7 @@
         <v>121513982</v>
       </c>
       <c r="B57" t="n">
-        <v>91160</v>
+        <v>91168</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>121528011</v>
       </c>
       <c r="B58" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>121216543</v>
       </c>
       <c r="B59" t="n">
-        <v>56560</v>
+        <v>56561</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 50245-2024 artfynd.xlsx
+++ b/artfynd/A 50245-2024 artfynd.xlsx
@@ -6844,7 +6844,7 @@
         <v>127085263</v>
       </c>
       <c r="B62" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
